--- a/research/traditional_assets/database/data/south_korea/south_korea_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_coal_related_energy.xlsx
@@ -1279,7 +1279,7 @@
         <v>90</v>
       </c>
       <c r="L2">
-        <v>60.3124732944968</v>
+        <v>60.3124732944969</v>
       </c>
       <c r="M2">
         <v>109.5</v>
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0998805156388326</v>
+        <v>0.0996645643497355</v>
       </c>
       <c r="C2">
-        <v>115.1263118700103</v>
+        <v>114.3233601351887</v>
       </c>
       <c r="D2">
-        <v>103.0263118700103</v>
+        <v>103.4393601351887</v>
       </c>
       <c r="E2">
-        <v>-31.6</v>
+        <v>-30.384</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.216</v>
       </c>
       <c r="G2">
         <v>12.1</v>
@@ -1579,28 +1579,28 @@
         <v>21.58</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0611648</v>
       </c>
       <c r="N2">
-        <v>21.58</v>
+        <v>21.5188352</v>
       </c>
       <c r="O2">
-        <v>5.395</v>
+        <v>5.3797088</v>
       </c>
       <c r="P2">
-        <v>16.185</v>
+        <v>16.1391264</v>
       </c>
       <c r="Q2">
-        <v>18.405</v>
+        <v>18.3591264</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0998805156388326</v>
+        <v>0.1002902165148843</v>
       </c>
       <c r="T2">
-        <v>1.083971466858168</v>
+        <v>1.092183371910124</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>352.8173066861986</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0996645643497355</v>
+        <v>0.09944861306063844</v>
       </c>
       <c r="C3">
-        <v>114.3233601351887</v>
+        <v>113.5237336794464</v>
       </c>
       <c r="D3">
-        <v>103.4393601351887</v>
+        <v>103.8557336794464</v>
       </c>
       <c r="E3">
-        <v>-30.384</v>
+        <v>-29.168</v>
       </c>
       <c r="F3">
-        <v>1.216</v>
+        <v>2.432</v>
       </c>
       <c r="G3">
         <v>12.1</v>
@@ -1661,28 +1661,28 @@
         <v>21.58</v>
       </c>
       <c r="M3">
-        <v>0.0611648</v>
+        <v>0.1223296</v>
       </c>
       <c r="N3">
-        <v>21.5188352</v>
+        <v>21.4576704</v>
       </c>
       <c r="O3">
-        <v>5.3797088</v>
+        <v>5.3644176</v>
       </c>
       <c r="P3">
-        <v>16.1391264</v>
+        <v>16.0932528</v>
       </c>
       <c r="Q3">
-        <v>18.3591264</v>
+        <v>18.3132528</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1002902165148843</v>
+        <v>0.1007082786333045</v>
       </c>
       <c r="T3">
-        <v>1.092183371910124</v>
+        <v>1.1005628668611</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>352.8173066861986</v>
+        <v>176.4086533430993</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09944861306063844</v>
+        <v>0.09923266177154136</v>
       </c>
       <c r="C4">
-        <v>113.5237336794464</v>
+        <v>112.7274728207247</v>
       </c>
       <c r="D4">
-        <v>103.8557336794464</v>
+        <v>104.2754728207247</v>
       </c>
       <c r="E4">
-        <v>-29.168</v>
+        <v>-27.952</v>
       </c>
       <c r="F4">
-        <v>2.432</v>
+        <v>3.648</v>
       </c>
       <c r="G4">
         <v>12.1</v>
@@ -1743,28 +1743,28 @@
         <v>21.58</v>
       </c>
       <c r="M4">
-        <v>0.1223296</v>
+        <v>0.1834944</v>
       </c>
       <c r="N4">
-        <v>21.4576704</v>
+        <v>21.3965056</v>
       </c>
       <c r="O4">
-        <v>5.3644176</v>
+        <v>5.3491264</v>
       </c>
       <c r="P4">
-        <v>16.0932528</v>
+        <v>16.0473792</v>
       </c>
       <c r="Q4">
-        <v>18.3132528</v>
+        <v>18.2673792</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1007082786333045</v>
+        <v>0.1011349605892179</v>
       </c>
       <c r="T4">
-        <v>1.1005628668611</v>
+        <v>1.109115134903847</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>176.4086533430993</v>
+        <v>117.6057688953995</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09923266177154136</v>
+        <v>0.09901671048244425</v>
       </c>
       <c r="C5">
-        <v>112.7274728207247</v>
+        <v>111.934618531399</v>
       </c>
       <c r="D5">
-        <v>104.2754728207247</v>
+        <v>104.698618531399</v>
       </c>
       <c r="E5">
-        <v>-27.952</v>
+        <v>-26.736</v>
       </c>
       <c r="F5">
-        <v>3.648</v>
+        <v>4.864</v>
       </c>
       <c r="G5">
         <v>12.1</v>
@@ -1825,28 +1825,28 @@
         <v>21.58</v>
       </c>
       <c r="M5">
-        <v>0.1834944</v>
+        <v>0.2446592</v>
       </c>
       <c r="N5">
-        <v>21.3965056</v>
+        <v>21.3353408</v>
       </c>
       <c r="O5">
-        <v>5.3491264</v>
+        <v>5.3338352</v>
       </c>
       <c r="P5">
-        <v>16.0473792</v>
+        <v>16.0015056</v>
       </c>
       <c r="Q5">
-        <v>18.2673792</v>
+        <v>18.2215056</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1011349605892179</v>
+        <v>0.1015705317525461</v>
       </c>
       <c r="T5">
-        <v>1.109115134903847</v>
+        <v>1.117845575197486</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>117.6057688953995</v>
+        <v>88.20432667154965</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09901671048244425</v>
+        <v>0.09880075919334719</v>
       </c>
       <c r="C6">
-        <v>111.934618531399</v>
+        <v>111.1452124516117</v>
       </c>
       <c r="D6">
-        <v>104.698618531399</v>
+        <v>105.1252124516117</v>
       </c>
       <c r="E6">
-        <v>-26.736</v>
+        <v>-25.52</v>
       </c>
       <c r="F6">
-        <v>4.864</v>
+        <v>6.08</v>
       </c>
       <c r="G6">
         <v>12.1</v>
@@ -1907,28 +1907,28 @@
         <v>21.58</v>
       </c>
       <c r="M6">
-        <v>0.2446592</v>
+        <v>0.305824</v>
       </c>
       <c r="N6">
-        <v>21.3353408</v>
+        <v>21.274176</v>
       </c>
       <c r="O6">
-        <v>5.3338352</v>
+        <v>5.318544</v>
       </c>
       <c r="P6">
-        <v>16.0015056</v>
+        <v>15.955632</v>
       </c>
       <c r="Q6">
-        <v>18.2215056</v>
+        <v>18.175632</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1015705317525461</v>
+        <v>0.1020152728351023</v>
       </c>
       <c r="T6">
-        <v>1.117845575197486</v>
+        <v>1.126759814234149</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>88.20432667154965</v>
+        <v>70.56346133723973</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09880075919334719</v>
+        <v>0.09858480790425009</v>
       </c>
       <c r="C7">
-        <v>111.1452124516117</v>
+        <v>110.3592969029317</v>
       </c>
       <c r="D7">
-        <v>105.1252124516117</v>
+        <v>105.5552969029317</v>
       </c>
       <c r="E7">
-        <v>-25.52</v>
+        <v>-24.304</v>
       </c>
       <c r="F7">
-        <v>6.08</v>
+        <v>7.296</v>
       </c>
       <c r="G7">
         <v>12.1</v>
@@ -1989,28 +1989,28 @@
         <v>21.58</v>
       </c>
       <c r="M7">
-        <v>0.305824</v>
+        <v>0.3669888</v>
       </c>
       <c r="N7">
-        <v>21.274176</v>
+        <v>21.2130112</v>
       </c>
       <c r="O7">
-        <v>5.318544</v>
+        <v>5.3032528</v>
       </c>
       <c r="P7">
-        <v>15.955632</v>
+        <v>15.9097584</v>
       </c>
       <c r="Q7">
-        <v>18.175632</v>
+        <v>18.1297584</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1020152728351023</v>
+        <v>0.1024694764938831</v>
       </c>
       <c r="T7">
-        <v>1.126759814234149</v>
+        <v>1.135863717931166</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>70.56346133723973</v>
+        <v>58.80288444769977</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09858480790425009</v>
+        <v>0.09836885661515302</v>
       </c>
       <c r="C8">
-        <v>110.3592969029317</v>
+        <v>109.5769149023508</v>
       </c>
       <c r="D8">
-        <v>105.5552969029317</v>
+        <v>105.9889149023508</v>
       </c>
       <c r="E8">
-        <v>-24.304</v>
+        <v>-23.088</v>
       </c>
       <c r="F8">
-        <v>7.295999999999999</v>
+        <v>8.511999999999999</v>
       </c>
       <c r="G8">
         <v>12.1</v>
@@ -2071,28 +2071,28 @@
         <v>21.58</v>
       </c>
       <c r="M8">
-        <v>0.3669887999999999</v>
+        <v>0.4281535999999999</v>
       </c>
       <c r="N8">
-        <v>21.2130112</v>
+        <v>21.1518464</v>
       </c>
       <c r="O8">
-        <v>5.3032528</v>
+        <v>5.287961600000001</v>
       </c>
       <c r="P8">
-        <v>15.9097584</v>
+        <v>15.8638848</v>
       </c>
       <c r="Q8">
-        <v>18.1297584</v>
+        <v>18.0838848</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1024694764938831</v>
+        <v>0.1029334479732828</v>
       </c>
       <c r="T8">
-        <v>1.135863717931166</v>
+        <v>1.145163404503387</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>58.80288444769977</v>
+        <v>50.40247238374268</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.098368856615153</v>
+        <v>0.09815290532605594</v>
       </c>
       <c r="C9">
-        <v>109.5769149023508</v>
+        <v>108.7981101766267</v>
       </c>
       <c r="D9">
-        <v>105.9889149023508</v>
+        <v>106.4261101766267</v>
       </c>
       <c r="E9">
-        <v>-23.088</v>
+        <v>-21.872</v>
       </c>
       <c r="F9">
-        <v>8.512</v>
+        <v>9.728</v>
       </c>
       <c r="G9">
         <v>12.1</v>
@@ -2153,28 +2153,28 @@
         <v>21.58</v>
       </c>
       <c r="M9">
-        <v>0.4281536</v>
+        <v>0.4893184</v>
       </c>
       <c r="N9">
-        <v>21.1518464</v>
+        <v>21.0906816</v>
       </c>
       <c r="O9">
-        <v>5.2879616</v>
+        <v>5.272670400000001</v>
       </c>
       <c r="P9">
-        <v>15.8638848</v>
+        <v>15.8180112</v>
       </c>
       <c r="Q9">
-        <v>18.0838848</v>
+        <v>18.0380112</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1029334479732828</v>
+        <v>0.1034075057891913</v>
       </c>
       <c r="T9">
-        <v>1.145163404503387</v>
+        <v>1.154665258175005</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>50.40247238374265</v>
+        <v>44.10216333577483</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09815290532605594</v>
+        <v>0.09793695403695886</v>
       </c>
       <c r="C10">
-        <v>108.7981101766267</v>
+        <v>108.0229271769819</v>
       </c>
       <c r="D10">
-        <v>106.4261101766267</v>
+        <v>106.8669271769819</v>
       </c>
       <c r="E10">
-        <v>-21.872</v>
+        <v>-20.656</v>
       </c>
       <c r="F10">
-        <v>9.728</v>
+        <v>10.944</v>
       </c>
       <c r="G10">
         <v>12.1</v>
@@ -2235,28 +2235,28 @@
         <v>21.58</v>
       </c>
       <c r="M10">
-        <v>0.4893184</v>
+        <v>0.5504832</v>
       </c>
       <c r="N10">
-        <v>21.0906816</v>
+        <v>21.0295168</v>
       </c>
       <c r="O10">
-        <v>5.272670400000001</v>
+        <v>5.257379200000001</v>
       </c>
       <c r="P10">
-        <v>15.8180112</v>
+        <v>15.7721376</v>
       </c>
       <c r="Q10">
-        <v>18.0380112</v>
+        <v>17.9921376</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1034075057891913</v>
+        <v>0.1038919824581965</v>
       </c>
       <c r="T10">
-        <v>1.154665258175005</v>
+        <v>1.16437594379545</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>44.10216333577483</v>
+        <v>39.20192296513319</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09793695403695886</v>
+        <v>0.09772100274786179</v>
       </c>
       <c r="C11">
-        <v>108.0229271769819</v>
+        <v>107.2514110941702</v>
       </c>
       <c r="D11">
-        <v>106.8669271769819</v>
+        <v>107.3114110941702</v>
       </c>
       <c r="E11">
-        <v>-20.656</v>
+        <v>-19.44</v>
       </c>
       <c r="F11">
-        <v>10.944</v>
+        <v>12.16</v>
       </c>
       <c r="G11">
         <v>12.1</v>
@@ -2317,28 +2317,28 @@
         <v>21.58</v>
       </c>
       <c r="M11">
-        <v>0.5504832</v>
+        <v>0.6116479999999999</v>
       </c>
       <c r="N11">
-        <v>21.0295168</v>
+        <v>20.968352</v>
       </c>
       <c r="O11">
-        <v>5.257379200000001</v>
+        <v>5.242088000000001</v>
       </c>
       <c r="P11">
-        <v>15.7721376</v>
+        <v>15.726264</v>
       </c>
       <c r="Q11">
-        <v>17.9921376</v>
+        <v>17.946264</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1038919824581965</v>
+        <v>0.104387225275402</v>
       </c>
       <c r="T11">
-        <v>1.16437594379545</v>
+        <v>1.174302422429682</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>39.20192296513319</v>
+        <v>35.28173066861987</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09772100274786179</v>
+        <v>0.0975050514587647</v>
       </c>
       <c r="C12">
-        <v>107.2514110941702</v>
+        <v>106.4836078739199</v>
       </c>
       <c r="D12">
-        <v>107.3114110941702</v>
+        <v>107.7596078739199</v>
       </c>
       <c r="E12">
-        <v>-19.44</v>
+        <v>-18.224</v>
       </c>
       <c r="F12">
-        <v>12.16</v>
+        <v>13.376</v>
       </c>
       <c r="G12">
         <v>12.1</v>
@@ -2399,28 +2399,28 @@
         <v>21.58</v>
       </c>
       <c r="M12">
-        <v>0.611648</v>
+        <v>0.6728128</v>
       </c>
       <c r="N12">
-        <v>20.968352</v>
+        <v>20.9071872</v>
       </c>
       <c r="O12">
-        <v>5.242088000000001</v>
+        <v>5.226796800000001</v>
       </c>
       <c r="P12">
-        <v>15.726264</v>
+        <v>15.6803904</v>
       </c>
       <c r="Q12">
-        <v>17.946264</v>
+        <v>17.9003904</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.104387225275402</v>
+        <v>0.1048935971446794</v>
       </c>
       <c r="T12">
-        <v>1.174302422429682</v>
+        <v>1.184451967999516</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>35.28173066861986</v>
+        <v>32.07430060783624</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0975050514587647</v>
+        <v>0.09728910016966763</v>
       </c>
       <c r="C13">
-        <v>106.4836078739199</v>
+        <v>105.7195642327664</v>
       </c>
       <c r="D13">
-        <v>107.7596078739199</v>
+        <v>108.2115642327664</v>
       </c>
       <c r="E13">
-        <v>-18.224</v>
+        <v>-17.008</v>
       </c>
       <c r="F13">
-        <v>13.376</v>
+        <v>14.592</v>
       </c>
       <c r="G13">
         <v>12.1</v>
@@ -2481,28 +2481,28 @@
         <v>21.58</v>
       </c>
       <c r="M13">
-        <v>0.6728128</v>
+        <v>0.7339775999999999</v>
       </c>
       <c r="N13">
-        <v>20.9071872</v>
+        <v>20.8460224</v>
       </c>
       <c r="O13">
-        <v>5.226796800000001</v>
+        <v>5.211505600000001</v>
       </c>
       <c r="P13">
-        <v>15.6803904</v>
+        <v>15.6345168</v>
       </c>
       <c r="Q13">
-        <v>17.9003904</v>
+        <v>17.8545168</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1048935971446794</v>
+        <v>0.1054114774655314</v>
       </c>
       <c r="T13">
-        <v>1.184451967999516</v>
+        <v>1.194832185059572</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.07430060783624</v>
+        <v>29.40144222384989</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09728910016966763</v>
+        <v>0.09707314888057053</v>
       </c>
       <c r="C14">
-        <v>105.7195642327664</v>
+        <v>104.9593276742846</v>
       </c>
       <c r="D14">
-        <v>108.2115642327664</v>
+        <v>108.6673276742846</v>
       </c>
       <c r="E14">
-        <v>-17.008</v>
+        <v>-15.792</v>
       </c>
       <c r="F14">
-        <v>14.592</v>
+        <v>15.808</v>
       </c>
       <c r="G14">
         <v>12.1</v>
@@ -2563,28 +2563,28 @@
         <v>21.58</v>
       </c>
       <c r="M14">
-        <v>0.7339775999999999</v>
+        <v>0.7951423999999999</v>
       </c>
       <c r="N14">
-        <v>20.8460224</v>
+        <v>20.7848576</v>
       </c>
       <c r="O14">
-        <v>5.211505600000001</v>
+        <v>5.196214400000001</v>
       </c>
       <c r="P14">
-        <v>15.6345168</v>
+        <v>15.5886432</v>
       </c>
       <c r="Q14">
-        <v>17.8545168</v>
+        <v>17.8086432</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1054114774655314</v>
+        <v>0.1059412630811156</v>
       </c>
       <c r="T14">
-        <v>1.194832185059572</v>
+        <v>1.20545102779917</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.40144222384989</v>
+        <v>27.13979282201528</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09707314888057053</v>
+        <v>0.09685719759147345</v>
       </c>
       <c r="C15">
-        <v>104.9593276742846</v>
+        <v>104.2029465057325</v>
       </c>
       <c r="D15">
-        <v>108.6673276742846</v>
+        <v>109.1269465057325</v>
       </c>
       <c r="E15">
-        <v>-15.792</v>
+        <v>-14.576</v>
       </c>
       <c r="F15">
-        <v>15.808</v>
+        <v>17.024</v>
       </c>
       <c r="G15">
         <v>12.1</v>
@@ -2645,28 +2645,28 @@
         <v>21.58</v>
       </c>
       <c r="M15">
-        <v>0.7951423999999999</v>
+        <v>0.8563072</v>
       </c>
       <c r="N15">
-        <v>20.7848576</v>
+        <v>20.7236928</v>
       </c>
       <c r="O15">
-        <v>5.196214400000001</v>
+        <v>5.180923200000001</v>
       </c>
       <c r="P15">
-        <v>15.5886432</v>
+        <v>15.5427696</v>
       </c>
       <c r="Q15">
-        <v>17.8086432</v>
+        <v>17.7627696</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1059412630811156</v>
+        <v>0.106483369292411</v>
       </c>
       <c r="T15">
-        <v>1.20545102779917</v>
+        <v>1.216316820369922</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.13979282201528</v>
+        <v>25.20123619187133</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09685719759147345</v>
+        <v>0.09664124630237637</v>
       </c>
       <c r="C16">
-        <v>104.2029465057325</v>
+        <v>103.4504698551205</v>
       </c>
       <c r="D16">
-        <v>109.1269465057325</v>
+        <v>109.5904698551205</v>
       </c>
       <c r="E16">
-        <v>-14.576</v>
+        <v>-13.36</v>
       </c>
       <c r="F16">
-        <v>17.024</v>
+        <v>18.24</v>
       </c>
       <c r="G16">
         <v>12.1</v>
@@ -2727,28 +2727,28 @@
         <v>21.58</v>
       </c>
       <c r="M16">
-        <v>0.8563072</v>
+        <v>0.9174720000000001</v>
       </c>
       <c r="N16">
-        <v>20.7236928</v>
+        <v>20.662528</v>
       </c>
       <c r="O16">
-        <v>5.180923200000001</v>
+        <v>5.165632</v>
       </c>
       <c r="P16">
-        <v>15.5427696</v>
+        <v>15.496896</v>
       </c>
       <c r="Q16">
-        <v>17.7627696</v>
+        <v>17.716896</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.106483369292411</v>
+        <v>0.1070382309439722</v>
       </c>
       <c r="T16">
-        <v>1.216316820369922</v>
+        <v>1.22743827864822</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.20123619187133</v>
+        <v>23.52115377907991</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09664124630237637</v>
+        <v>0.09642529501327929</v>
       </c>
       <c r="C17">
-        <v>103.4504698551205</v>
+        <v>102.7019476887165</v>
       </c>
       <c r="D17">
-        <v>109.5904698551205</v>
+        <v>110.0579476887165</v>
       </c>
       <c r="E17">
-        <v>-13.36</v>
+        <v>-12.144</v>
       </c>
       <c r="F17">
-        <v>18.24</v>
+        <v>19.456</v>
       </c>
       <c r="G17">
         <v>12.1</v>
@@ -2809,28 +2809,28 @@
         <v>21.58</v>
       </c>
       <c r="M17">
-        <v>0.9174719999999998</v>
+        <v>0.9786368</v>
       </c>
       <c r="N17">
-        <v>20.662528</v>
+        <v>20.6013632</v>
       </c>
       <c r="O17">
-        <v>5.165632</v>
+        <v>5.1503408</v>
       </c>
       <c r="P17">
-        <v>15.496896</v>
+        <v>15.4510224</v>
       </c>
       <c r="Q17">
-        <v>17.716896</v>
+        <v>17.6710224</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1070382309439722</v>
+        <v>0.1076063035872372</v>
       </c>
       <c r="T17">
-        <v>1.22743827864822</v>
+        <v>1.238824533552192</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.52115377907991</v>
+        <v>22.05108166788741</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09642529501327929</v>
+        <v>0.0962093437241822</v>
       </c>
       <c r="C18">
-        <v>102.7019476887165</v>
+        <v>101.957430829001</v>
       </c>
       <c r="D18">
-        <v>110.0579476887165</v>
+        <v>110.529430829001</v>
       </c>
       <c r="E18">
-        <v>-12.144</v>
+        <v>-10.928</v>
       </c>
       <c r="F18">
-        <v>19.456</v>
+        <v>20.672</v>
       </c>
       <c r="G18">
         <v>12.1</v>
@@ -2891,28 +2891,28 @@
         <v>21.58</v>
       </c>
       <c r="M18">
-        <v>0.9786368</v>
+        <v>1.0398016</v>
       </c>
       <c r="N18">
-        <v>20.6013632</v>
+        <v>20.5401984</v>
       </c>
       <c r="O18">
-        <v>5.1503408</v>
+        <v>5.1350496</v>
       </c>
       <c r="P18">
-        <v>15.4510224</v>
+        <v>15.4051488</v>
       </c>
       <c r="Q18">
-        <v>17.6710224</v>
+        <v>17.6251488</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1076063035872372</v>
+        <v>0.1081880647279304</v>
       </c>
       <c r="T18">
-        <v>1.238824533552192</v>
+        <v>1.250485156044213</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.05108166788741</v>
+        <v>20.75395921683522</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0962093437241822</v>
+        <v>0.09599339243508512</v>
       </c>
       <c r="C19">
-        <v>101.957430829001</v>
+        <v>101.2169709730859</v>
       </c>
       <c r="D19">
-        <v>110.529430829001</v>
+        <v>111.0049709730859</v>
       </c>
       <c r="E19">
-        <v>-10.928</v>
+        <v>-9.711999999999996</v>
       </c>
       <c r="F19">
-        <v>20.672</v>
+        <v>21.888</v>
       </c>
       <c r="G19">
         <v>12.1</v>
@@ -2973,28 +2973,28 @@
         <v>21.58</v>
       </c>
       <c r="M19">
-        <v>1.0398016</v>
+        <v>1.1009664</v>
       </c>
       <c r="N19">
-        <v>20.5401984</v>
+        <v>20.4790336</v>
       </c>
       <c r="O19">
-        <v>5.1350496</v>
+        <v>5.1197584</v>
       </c>
       <c r="P19">
-        <v>15.4051488</v>
+        <v>15.3592752</v>
       </c>
       <c r="Q19">
-        <v>17.6251488</v>
+        <v>17.5792752</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1081880647279304</v>
+        <v>0.108784015164738</v>
       </c>
       <c r="T19">
-        <v>1.250485156044213</v>
+        <v>1.262430183962867</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.75395921683522</v>
+        <v>19.60096148256659</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09599339243508513</v>
+        <v>0.09577744114598805</v>
       </c>
       <c r="C20">
-        <v>101.2169709730859</v>
+        <v>100.4806207116109</v>
       </c>
       <c r="D20">
-        <v>111.0049709730859</v>
+        <v>111.4846207116109</v>
       </c>
       <c r="E20">
-        <v>-9.712</v>
+        <v>-8.495999999999999</v>
       </c>
       <c r="F20">
-        <v>21.888</v>
+        <v>23.104</v>
       </c>
       <c r="G20">
         <v>12.1</v>
@@ -3055,28 +3055,28 @@
         <v>21.58</v>
       </c>
       <c r="M20">
-        <v>1.1009664</v>
+        <v>1.1621312</v>
       </c>
       <c r="N20">
-        <v>20.4790336</v>
+        <v>20.4178688</v>
       </c>
       <c r="O20">
-        <v>5.1197584</v>
+        <v>5.1044672</v>
       </c>
       <c r="P20">
-        <v>15.3592752</v>
+        <v>15.3134016</v>
       </c>
       <c r="Q20">
-        <v>17.5792752</v>
+        <v>17.5334016</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.108784015164738</v>
+        <v>0.1093946804271457</v>
       </c>
       <c r="T20">
-        <v>1.262430183962867</v>
+        <v>1.274670150842476</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.60096148256659</v>
+        <v>18.56933193085256</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09577744114598805</v>
+        <v>0.09556148985689097</v>
       </c>
       <c r="C21">
-        <v>100.4806207116109</v>
+        <v>99.74843354813186</v>
       </c>
       <c r="D21">
-        <v>111.4846207116109</v>
+        <v>111.9684335481319</v>
       </c>
       <c r="E21">
-        <v>-8.495999999999999</v>
+        <v>-7.279999999999998</v>
       </c>
       <c r="F21">
-        <v>23.104</v>
+        <v>24.32</v>
       </c>
       <c r="G21">
         <v>12.1</v>
@@ -3137,28 +3137,28 @@
         <v>21.58</v>
       </c>
       <c r="M21">
-        <v>1.1621312</v>
+        <v>1.223296</v>
       </c>
       <c r="N21">
-        <v>20.4178688</v>
+        <v>20.356704</v>
       </c>
       <c r="O21">
-        <v>5.1044672</v>
+        <v>5.089176</v>
       </c>
       <c r="P21">
-        <v>15.3134016</v>
+        <v>15.267528</v>
       </c>
       <c r="Q21">
-        <v>17.5334016</v>
+        <v>17.487528</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1093946804271457</v>
+        <v>0.1100206123211137</v>
       </c>
       <c r="T21">
-        <v>1.274670150842476</v>
+        <v>1.287216116894075</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.56933193085256</v>
+        <v>17.64086533430993</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09556148985689097</v>
+        <v>0.0953455385677939</v>
       </c>
       <c r="C22">
-        <v>99.74843354813186</v>
+        <v>99.02046391901608</v>
       </c>
       <c r="D22">
-        <v>111.9684335481319</v>
+        <v>112.4564639190161</v>
       </c>
       <c r="E22">
-        <v>-7.279999999999998</v>
+        <v>-6.063999999999997</v>
       </c>
       <c r="F22">
-        <v>24.32</v>
+        <v>25.536</v>
       </c>
       <c r="G22">
         <v>12.1</v>
@@ -3219,28 +3219,28 @@
         <v>21.58</v>
       </c>
       <c r="M22">
-        <v>1.223296</v>
+        <v>1.2844608</v>
       </c>
       <c r="N22">
-        <v>20.356704</v>
+        <v>20.2955392</v>
       </c>
       <c r="O22">
-        <v>5.089176</v>
+        <v>5.0738848</v>
       </c>
       <c r="P22">
-        <v>15.267528</v>
+        <v>15.2216544</v>
       </c>
       <c r="Q22">
-        <v>17.487528</v>
+        <v>17.4416544</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1100206123211137</v>
+        <v>0.1106623905921442</v>
       </c>
       <c r="T22">
-        <v>1.287216116894075</v>
+        <v>1.300079702339386</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.64086533430993</v>
+        <v>16.80082412791422</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0953455385677939</v>
+        <v>0.09512958727869682</v>
       </c>
       <c r="C23">
-        <v>99.02046391901608</v>
+        <v>98.29676721386036</v>
       </c>
       <c r="D23">
-        <v>112.4564639190161</v>
+        <v>112.9487672138604</v>
       </c>
       <c r="E23">
-        <v>-6.064</v>
+        <v>-4.847999999999999</v>
       </c>
       <c r="F23">
-        <v>25.536</v>
+        <v>26.752</v>
       </c>
       <c r="G23">
         <v>12.1</v>
@@ -3301,28 +3301,28 @@
         <v>21.58</v>
       </c>
       <c r="M23">
-        <v>1.2844608</v>
+        <v>1.3456256</v>
       </c>
       <c r="N23">
-        <v>20.2955392</v>
+        <v>20.2343744</v>
       </c>
       <c r="O23">
-        <v>5.0738848</v>
+        <v>5.0585936</v>
       </c>
       <c r="P23">
-        <v>15.2216544</v>
+        <v>15.1757808</v>
       </c>
       <c r="Q23">
-        <v>17.4416544</v>
+        <v>17.3957808</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1106623905921442</v>
+        <v>0.111320624716278</v>
       </c>
       <c r="T23">
-        <v>1.300079702339386</v>
+        <v>1.313273123308935</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.80082412791422</v>
+        <v>16.03715030391812</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09512958727869682</v>
+        <v>0.0949136359895997</v>
       </c>
       <c r="C24">
-        <v>98.29676721386036</v>
+        <v>97.57739979644757</v>
       </c>
       <c r="D24">
-        <v>112.9487672138604</v>
+        <v>113.4453997964476</v>
       </c>
       <c r="E24">
-        <v>-4.847999999999999</v>
+        <v>-3.631999999999998</v>
       </c>
       <c r="F24">
-        <v>26.752</v>
+        <v>27.968</v>
       </c>
       <c r="G24">
         <v>12.1</v>
@@ -3383,28 +3383,28 @@
         <v>21.58</v>
       </c>
       <c r="M24">
-        <v>1.3456256</v>
+        <v>1.4067904</v>
       </c>
       <c r="N24">
-        <v>20.2343744</v>
+        <v>20.1732096</v>
       </c>
       <c r="O24">
-        <v>5.0585936</v>
+        <v>5.043302400000001</v>
       </c>
       <c r="P24">
-        <v>15.1757808</v>
+        <v>15.1299072</v>
       </c>
       <c r="Q24">
-        <v>17.3957808</v>
+        <v>17.3499072</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.111320624716278</v>
+        <v>0.111995955830649</v>
       </c>
       <c r="T24">
-        <v>1.313273123308935</v>
+        <v>1.326809230537433</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.03715030391812</v>
+        <v>15.33988289939994</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0949136359895997</v>
+        <v>0.09469768470050263</v>
       </c>
       <c r="C25">
-        <v>97.57739979644757</v>
+        <v>96.86241902625834</v>
       </c>
       <c r="D25">
-        <v>113.4453997964476</v>
+        <v>113.9464190262583</v>
       </c>
       <c r="E25">
-        <v>-3.631999999999998</v>
+        <v>-2.415999999999997</v>
       </c>
       <c r="F25">
-        <v>27.968</v>
+        <v>29.184</v>
       </c>
       <c r="G25">
         <v>12.1</v>
@@ -3465,28 +3465,28 @@
         <v>21.58</v>
       </c>
       <c r="M25">
-        <v>1.4067904</v>
+        <v>1.4679552</v>
       </c>
       <c r="N25">
-        <v>20.1732096</v>
+        <v>20.1120448</v>
       </c>
       <c r="O25">
-        <v>5.043302400000001</v>
+        <v>5.028011200000001</v>
       </c>
       <c r="P25">
-        <v>15.1299072</v>
+        <v>15.0840336</v>
       </c>
       <c r="Q25">
-        <v>17.3499072</v>
+        <v>17.3040336</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.111995955830649</v>
+        <v>0.1126890588164508</v>
       </c>
       <c r="T25">
-        <v>1.326809230537433</v>
+        <v>1.34070155111405</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.33988289939994</v>
+        <v>14.70072111192494</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09469768470050263</v>
+        <v>0.09448173341140556</v>
       </c>
       <c r="C26">
-        <v>96.86241902625834</v>
+        <v>96.15188328055604</v>
       </c>
       <c r="D26">
-        <v>113.9464190262583</v>
+        <v>114.451883280556</v>
       </c>
       <c r="E26">
-        <v>-2.416</v>
+        <v>-1.199999999999999</v>
       </c>
       <c r="F26">
-        <v>29.184</v>
+        <v>30.4</v>
       </c>
       <c r="G26">
         <v>12.1</v>
@@ -3547,28 +3547,28 @@
         <v>21.58</v>
       </c>
       <c r="M26">
-        <v>1.4679552</v>
+        <v>1.52912</v>
       </c>
       <c r="N26">
-        <v>20.1120448</v>
+        <v>20.05088</v>
       </c>
       <c r="O26">
-        <v>5.028011200000001</v>
+        <v>5.012720000000001</v>
       </c>
       <c r="P26">
-        <v>15.0840336</v>
+        <v>15.03816</v>
       </c>
       <c r="Q26">
-        <v>17.3040336</v>
+        <v>17.25816</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1126890588164508</v>
+        <v>0.1134006445485407</v>
       </c>
       <c r="T26">
-        <v>1.34070155111405</v>
+        <v>1.35496433357271</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.70072111192495</v>
+        <v>14.11269226744795</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09448173341140556</v>
+        <v>0.09426578212230848</v>
       </c>
       <c r="C27">
-        <v>96.15188328055604</v>
+        <v>95.44585197706137</v>
       </c>
       <c r="D27">
-        <v>114.451883280556</v>
+        <v>114.9618519770614</v>
       </c>
       <c r="E27">
-        <v>-1.199999999999999</v>
+        <v>0.01600000000000179</v>
       </c>
       <c r="F27">
-        <v>30.4</v>
+        <v>31.616</v>
       </c>
       <c r="G27">
         <v>12.1</v>
@@ -3629,28 +3629,28 @@
         <v>21.58</v>
       </c>
       <c r="M27">
-        <v>1.52912</v>
+        <v>1.5902848</v>
       </c>
       <c r="N27">
-        <v>20.05088</v>
+        <v>19.9897152</v>
       </c>
       <c r="O27">
-        <v>5.012720000000001</v>
+        <v>4.997428800000001</v>
       </c>
       <c r="P27">
-        <v>15.03816</v>
+        <v>14.9922864</v>
       </c>
       <c r="Q27">
-        <v>17.25816</v>
+        <v>17.2122864</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1134006445485407</v>
+        <v>0.1141314623274439</v>
       </c>
       <c r="T27">
-        <v>1.35496433357271</v>
+        <v>1.369612596638361</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.11269226744795</v>
+        <v>13.56989641100764</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09426578212230848</v>
+        <v>0.0940498308332114</v>
       </c>
       <c r="C28">
-        <v>95.44585197706137</v>
+        <v>94.74438559723617</v>
       </c>
       <c r="D28">
-        <v>114.9618519770614</v>
+        <v>115.4763855972362</v>
       </c>
       <c r="E28">
-        <v>0.01600000000000179</v>
+        <v>1.232000000000003</v>
       </c>
       <c r="F28">
-        <v>31.616</v>
+        <v>32.832</v>
       </c>
       <c r="G28">
         <v>12.1</v>
@@ -3711,28 +3711,28 @@
         <v>21.58</v>
       </c>
       <c r="M28">
-        <v>1.5902848</v>
+        <v>1.6514496</v>
       </c>
       <c r="N28">
-        <v>19.9897152</v>
+        <v>19.9285504</v>
       </c>
       <c r="O28">
-        <v>4.997428800000001</v>
+        <v>4.982137600000001</v>
       </c>
       <c r="P28">
-        <v>14.9922864</v>
+        <v>14.9464128</v>
       </c>
       <c r="Q28">
-        <v>17.2122864</v>
+        <v>17.1664128</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1141314623274439</v>
+        <v>0.1148823025112485</v>
       </c>
       <c r="T28">
-        <v>1.369612596638361</v>
+        <v>1.384662181979784</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.56989641100764</v>
+        <v>13.0673076550444</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0940498308332114</v>
+        <v>0.09414887954411431</v>
       </c>
       <c r="C29">
-        <v>94.74438559723617</v>
+        <v>93.29181781653509</v>
       </c>
       <c r="D29">
-        <v>115.4763855972362</v>
+        <v>115.2398178165351</v>
       </c>
       <c r="E29">
-        <v>1.232000000000003</v>
+        <v>2.448000000000004</v>
       </c>
       <c r="F29">
-        <v>32.832</v>
+        <v>34.048</v>
       </c>
       <c r="G29">
         <v>12.1</v>
@@ -3793,45 +3793,45 @@
         <v>21.58</v>
       </c>
       <c r="M29">
-        <v>1.6514496</v>
+        <v>1.7636864</v>
       </c>
       <c r="N29">
-        <v>19.9285504</v>
+        <v>19.8163136</v>
       </c>
       <c r="O29">
-        <v>4.982137600000001</v>
+        <v>4.9540784</v>
       </c>
       <c r="P29">
-        <v>14.9464128</v>
+        <v>14.8622352</v>
       </c>
       <c r="Q29">
-        <v>17.1664128</v>
+        <v>17.0822352</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1148823025112485</v>
+        <v>0.1156539993668254</v>
       </c>
       <c r="T29">
-        <v>1.384662181979784</v>
+        <v>1.400129811358467</v>
       </c>
       <c r="U29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>13.0673076550444</v>
+        <v>12.23573533253984</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09414887954411431</v>
+        <v>0.09394417825501722</v>
       </c>
       <c r="C30">
-        <v>93.29181781653509</v>
+        <v>92.56579895480286</v>
       </c>
       <c r="D30">
-        <v>115.2398178165351</v>
+        <v>115.7297989548029</v>
       </c>
       <c r="E30">
-        <v>2.448000000000004</v>
+        <v>3.664000000000005</v>
       </c>
       <c r="F30">
-        <v>34.048</v>
+        <v>35.264</v>
       </c>
       <c r="G30">
         <v>12.1</v>
@@ -3875,28 +3875,28 @@
         <v>21.58</v>
       </c>
       <c r="M30">
-        <v>1.7636864</v>
+        <v>1.8266752</v>
       </c>
       <c r="N30">
-        <v>19.8163136</v>
+        <v>19.7533248</v>
       </c>
       <c r="O30">
-        <v>4.9540784</v>
+        <v>4.9383312</v>
       </c>
       <c r="P30">
-        <v>14.8622352</v>
+        <v>14.8149936</v>
       </c>
       <c r="Q30">
-        <v>17.0822352</v>
+        <v>17.0349936</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1156539993668254</v>
+        <v>0.1164474341619961</v>
       </c>
       <c r="T30">
-        <v>1.400129811358467</v>
+        <v>1.416033148606973</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.23573533253984</v>
+        <v>11.81381342452123</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09394417825501722</v>
+        <v>0.09373947696592014</v>
       </c>
       <c r="C31">
-        <v>92.56579895480286</v>
+        <v>91.84396452631788</v>
       </c>
       <c r="D31">
-        <v>115.7297989548029</v>
+        <v>116.2239645263179</v>
       </c>
       <c r="E31">
-        <v>3.663999999999998</v>
+        <v>4.879999999999999</v>
       </c>
       <c r="F31">
-        <v>35.264</v>
+        <v>36.48</v>
       </c>
       <c r="G31">
         <v>12.1</v>
@@ -3957,28 +3957,28 @@
         <v>21.58</v>
       </c>
       <c r="M31">
-        <v>1.8266752</v>
+        <v>1.889664</v>
       </c>
       <c r="N31">
-        <v>19.7533248</v>
+        <v>19.690336</v>
       </c>
       <c r="O31">
-        <v>4.9383312</v>
+        <v>4.922584000000001</v>
       </c>
       <c r="P31">
-        <v>14.8149936</v>
+        <v>14.767752</v>
       </c>
       <c r="Q31">
-        <v>17.0349936</v>
+        <v>16.987752</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1164474341619961</v>
+        <v>0.1172635385227431</v>
       </c>
       <c r="T31">
-        <v>1.416033148606973</v>
+        <v>1.432390866919723</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.81381342452123</v>
+        <v>11.42001964370386</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09373947696592014</v>
+        <v>0.09353477567682307</v>
       </c>
       <c r="C32">
-        <v>91.84396452631788</v>
+        <v>91.1263683634613</v>
       </c>
       <c r="D32">
-        <v>116.2239645263179</v>
+        <v>116.7223683634613</v>
       </c>
       <c r="E32">
-        <v>4.879999999999999</v>
+        <v>6.096</v>
       </c>
       <c r="F32">
-        <v>36.48</v>
+        <v>37.696</v>
       </c>
       <c r="G32">
         <v>12.1</v>
@@ -4039,28 +4039,28 @@
         <v>21.58</v>
       </c>
       <c r="M32">
-        <v>1.889664</v>
+        <v>1.9526528</v>
       </c>
       <c r="N32">
-        <v>19.690336</v>
+        <v>19.6273472</v>
       </c>
       <c r="O32">
-        <v>4.922584000000001</v>
+        <v>4.906836800000001</v>
       </c>
       <c r="P32">
-        <v>14.767752</v>
+        <v>14.7205104</v>
       </c>
       <c r="Q32">
-        <v>16.987752</v>
+        <v>16.9405104</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1172635385227431</v>
+        <v>0.1181032980823523</v>
       </c>
       <c r="T32">
-        <v>1.432390866919723</v>
+        <v>1.44922272199516</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.42001964370386</v>
+        <v>11.0516319132618</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09353477567682307</v>
+        <v>0.09333007438772598</v>
       </c>
       <c r="C33">
-        <v>91.1263683634613</v>
+        <v>90.41306522599001</v>
       </c>
       <c r="D33">
-        <v>116.7223683634613</v>
+        <v>117.22506522599</v>
       </c>
       <c r="E33">
-        <v>6.096</v>
+        <v>7.312000000000001</v>
       </c>
       <c r="F33">
-        <v>37.696</v>
+        <v>38.912</v>
       </c>
       <c r="G33">
         <v>12.1</v>
@@ -4121,28 +4121,28 @@
         <v>21.58</v>
       </c>
       <c r="M33">
-        <v>1.9526528</v>
+        <v>2.0156416</v>
       </c>
       <c r="N33">
-        <v>19.6273472</v>
+        <v>19.5643584</v>
       </c>
       <c r="O33">
-        <v>4.906836800000001</v>
+        <v>4.891089600000001</v>
       </c>
       <c r="P33">
-        <v>14.7205104</v>
+        <v>14.6732688</v>
       </c>
       <c r="Q33">
-        <v>16.9405104</v>
+        <v>16.8932688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1181032980823523</v>
+        <v>0.1189677564525382</v>
       </c>
       <c r="T33">
-        <v>1.44922272199516</v>
+        <v>1.46654963163164</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.0516319132618</v>
+        <v>10.70626841597237</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09333007438772598</v>
+        <v>0.09312537309862889</v>
       </c>
       <c r="C34">
-        <v>90.41306522599001</v>
+        <v>89.70411082109267</v>
       </c>
       <c r="D34">
-        <v>117.22506522599</v>
+        <v>117.7321108210927</v>
       </c>
       <c r="E34">
-        <v>7.312000000000001</v>
+        <v>8.528000000000002</v>
       </c>
       <c r="F34">
-        <v>38.912</v>
+        <v>40.128</v>
       </c>
       <c r="G34">
         <v>12.1</v>
@@ -4203,28 +4203,28 @@
         <v>21.58</v>
       </c>
       <c r="M34">
-        <v>2.0156416</v>
+        <v>2.0786304</v>
       </c>
       <c r="N34">
-        <v>19.5643584</v>
+        <v>19.5013696</v>
       </c>
       <c r="O34">
-        <v>4.891089600000001</v>
+        <v>4.875342400000001</v>
       </c>
       <c r="P34">
-        <v>14.6732688</v>
+        <v>14.6260272</v>
       </c>
       <c r="Q34">
-        <v>16.8932688</v>
+        <v>16.8460272</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1189677564525382</v>
+        <v>0.1198580195501924</v>
       </c>
       <c r="T34">
-        <v>1.46654963163164</v>
+        <v>1.484393762451298</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.70626841597237</v>
+        <v>10.38183603973078</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09312537309862889</v>
+        <v>0.09292067180953181</v>
       </c>
       <c r="C35">
-        <v>89.70411082109267</v>
+        <v>88.99956182396915</v>
       </c>
       <c r="D35">
-        <v>117.7321108210927</v>
+        <v>118.2435618239691</v>
       </c>
       <c r="E35">
-        <v>8.528000000000002</v>
+        <v>9.744000000000003</v>
       </c>
       <c r="F35">
-        <v>40.128</v>
+        <v>41.344</v>
       </c>
       <c r="G35">
         <v>12.1</v>
@@ -4285,28 +4285,28 @@
         <v>21.58</v>
       </c>
       <c r="M35">
-        <v>2.0786304</v>
+        <v>2.1416192</v>
       </c>
       <c r="N35">
-        <v>19.5013696</v>
+        <v>19.4383808</v>
       </c>
       <c r="O35">
-        <v>4.875342400000001</v>
+        <v>4.8595952</v>
       </c>
       <c r="P35">
-        <v>14.6260272</v>
+        <v>14.5787856</v>
       </c>
       <c r="Q35">
-        <v>16.8460272</v>
+        <v>16.7987856</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1198580195501924</v>
+        <v>0.1207752603174725</v>
       </c>
       <c r="T35">
-        <v>1.484393762451298</v>
+        <v>1.502778624507915</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.38183603973078</v>
+        <v>10.07648792091517</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09292067180953181</v>
+        <v>0.09316222052043474</v>
       </c>
       <c r="C36">
-        <v>88.99956182396915</v>
+        <v>87.1805161977864</v>
       </c>
       <c r="D36">
-        <v>118.2435618239691</v>
+        <v>117.6405161977864</v>
       </c>
       <c r="E36">
-        <v>9.744000000000003</v>
+        <v>10.96</v>
       </c>
       <c r="F36">
-        <v>41.344</v>
+        <v>42.56</v>
       </c>
       <c r="G36">
         <v>12.1</v>
@@ -4367,45 +4367,45 @@
         <v>21.58</v>
       </c>
       <c r="M36">
-        <v>2.1416192</v>
+        <v>2.27696</v>
       </c>
       <c r="N36">
-        <v>19.4383808</v>
+        <v>19.30304</v>
       </c>
       <c r="O36">
-        <v>4.8595952</v>
+        <v>4.825760000000001</v>
       </c>
       <c r="P36">
-        <v>14.5787856</v>
+        <v>14.47728</v>
       </c>
       <c r="Q36">
-        <v>16.7987856</v>
+        <v>16.69728</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1207752603174725</v>
+        <v>0.1217207238775919</v>
       </c>
       <c r="T36">
-        <v>1.502778624507915</v>
+        <v>1.521729174627813</v>
       </c>
       <c r="U36">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>10.07648792091517</v>
+        <v>9.477549012718715</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09316222052043474</v>
+        <v>0.09297026923133765</v>
       </c>
       <c r="C37">
-        <v>87.1805161977864</v>
+        <v>86.44323402370057</v>
       </c>
       <c r="D37">
-        <v>117.6405161977864</v>
+        <v>118.1192340237006</v>
       </c>
       <c r="E37">
-        <v>10.96</v>
+        <v>12.17600000000001</v>
       </c>
       <c r="F37">
-        <v>42.56</v>
+        <v>43.776</v>
       </c>
       <c r="G37">
         <v>12.1</v>
@@ -4449,28 +4449,28 @@
         <v>21.58</v>
       </c>
       <c r="M37">
-        <v>2.27696</v>
+        <v>2.342016</v>
       </c>
       <c r="N37">
-        <v>19.30304</v>
+        <v>19.237984</v>
       </c>
       <c r="O37">
-        <v>4.825760000000001</v>
+        <v>4.809496</v>
       </c>
       <c r="P37">
-        <v>14.47728</v>
+        <v>14.428488</v>
       </c>
       <c r="Q37">
-        <v>16.69728</v>
+        <v>16.648488</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1217207238775919</v>
+        <v>0.1226957331739651</v>
       </c>
       <c r="T37">
-        <v>1.521729174627813</v>
+        <v>1.541271929438958</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.477549012718715</v>
+        <v>9.214283762365415</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09297026923133767</v>
+        <v>0.09277831794224059</v>
       </c>
       <c r="C38">
-        <v>86.44323402370055</v>
+        <v>85.70986388852211</v>
       </c>
       <c r="D38">
-        <v>118.1192340237005</v>
+        <v>118.6018638885221</v>
       </c>
       <c r="E38">
-        <v>12.176</v>
+        <v>13.392</v>
       </c>
       <c r="F38">
-        <v>43.776</v>
+        <v>44.992</v>
       </c>
       <c r="G38">
         <v>12.1</v>
@@ -4531,28 +4531,28 @@
         <v>21.58</v>
       </c>
       <c r="M38">
-        <v>2.342016</v>
+        <v>2.407072</v>
       </c>
       <c r="N38">
-        <v>19.237984</v>
+        <v>19.172928</v>
       </c>
       <c r="O38">
-        <v>4.809496</v>
+        <v>4.793232000000001</v>
       </c>
       <c r="P38">
-        <v>14.428488</v>
+        <v>14.379696</v>
       </c>
       <c r="Q38">
-        <v>16.648488</v>
+        <v>16.599696</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1226957331739651</v>
+        <v>0.1237016951464136</v>
       </c>
       <c r="T38">
-        <v>1.541271929438958</v>
+        <v>1.561435089164743</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.214283762365417</v>
+        <v>8.965249066085271</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09277831794224059</v>
+        <v>0.0925863666531435</v>
       </c>
       <c r="C39">
-        <v>85.70986388852211</v>
+        <v>84.98045394223362</v>
       </c>
       <c r="D39">
-        <v>118.6018638885221</v>
+        <v>119.0884539422336</v>
       </c>
       <c r="E39">
-        <v>13.392</v>
+        <v>14.608</v>
       </c>
       <c r="F39">
-        <v>44.992</v>
+        <v>46.208</v>
       </c>
       <c r="G39">
         <v>12.1</v>
@@ -4613,28 +4613,28 @@
         <v>21.58</v>
       </c>
       <c r="M39">
-        <v>2.407072</v>
+        <v>2.472128</v>
       </c>
       <c r="N39">
-        <v>19.172928</v>
+        <v>19.107872</v>
       </c>
       <c r="O39">
-        <v>4.793232000000001</v>
+        <v>4.776968</v>
       </c>
       <c r="P39">
-        <v>14.379696</v>
+        <v>14.330904</v>
       </c>
       <c r="Q39">
-        <v>16.599696</v>
+        <v>16.550904</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1237016951464136</v>
+        <v>0.1247401075050702</v>
       </c>
       <c r="T39">
-        <v>1.561435089164743</v>
+        <v>1.58224867339781</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.965249066085271</v>
+        <v>8.729321459083026</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0925863666531435</v>
+        <v>0.09239441536404643</v>
       </c>
       <c r="C40">
-        <v>84.98045394223362</v>
+        <v>84.25505312825598</v>
       </c>
       <c r="D40">
-        <v>119.0884539422336</v>
+        <v>119.579053128256</v>
       </c>
       <c r="E40">
-        <v>14.608</v>
+        <v>15.824</v>
       </c>
       <c r="F40">
-        <v>46.208</v>
+        <v>47.424</v>
       </c>
       <c r="G40">
         <v>12.1</v>
@@ -4695,28 +4695,28 @@
         <v>21.58</v>
       </c>
       <c r="M40">
-        <v>2.472128</v>
+        <v>2.537184</v>
       </c>
       <c r="N40">
-        <v>19.107872</v>
+        <v>19.042816</v>
       </c>
       <c r="O40">
-        <v>4.776968</v>
+        <v>4.760704</v>
       </c>
       <c r="P40">
-        <v>14.330904</v>
+        <v>14.282112</v>
       </c>
       <c r="Q40">
-        <v>16.550904</v>
+        <v>16.502112</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1247401075050702</v>
+        <v>0.1258125661705679</v>
       </c>
       <c r="T40">
-        <v>1.58224867339781</v>
+        <v>1.603744670228683</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.729321459083026</v>
+        <v>8.505492703721924</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09239441536404643</v>
+        <v>0.09220246407494934</v>
       </c>
       <c r="C41">
-        <v>84.25505312825598</v>
+        <v>83.53371119985978</v>
       </c>
       <c r="D41">
-        <v>119.579053128256</v>
+        <v>120.0737111998598</v>
       </c>
       <c r="E41">
-        <v>15.824</v>
+        <v>17.04</v>
       </c>
       <c r="F41">
-        <v>47.424</v>
+        <v>48.64</v>
       </c>
       <c r="G41">
         <v>12.1</v>
@@ -4777,28 +4777,28 @@
         <v>21.58</v>
       </c>
       <c r="M41">
-        <v>2.537184</v>
+        <v>2.60224</v>
       </c>
       <c r="N41">
-        <v>19.042816</v>
+        <v>18.97776</v>
       </c>
       <c r="O41">
-        <v>4.760704</v>
+        <v>4.744440000000001</v>
       </c>
       <c r="P41">
-        <v>14.282112</v>
+        <v>14.23332</v>
       </c>
       <c r="Q41">
-        <v>16.502112</v>
+        <v>16.45332</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1258125661705679</v>
+        <v>0.1269207734582489</v>
       </c>
       <c r="T41">
-        <v>1.603744670228683</v>
+        <v>1.625957200287253</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.505492703721924</v>
+        <v>8.292855386128874</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09220246407494934</v>
+        <v>0.09201051278585225</v>
       </c>
       <c r="C42">
-        <v>83.53371119985978</v>
+        <v>82.81647873698481</v>
       </c>
       <c r="D42">
-        <v>120.0737111998598</v>
+        <v>120.5724787369848</v>
       </c>
       <c r="E42">
-        <v>17.04</v>
+        <v>18.256</v>
       </c>
       <c r="F42">
-        <v>48.64</v>
+        <v>49.856</v>
       </c>
       <c r="G42">
         <v>12.1</v>
@@ -4859,28 +4859,28 @@
         <v>21.58</v>
       </c>
       <c r="M42">
-        <v>2.60224</v>
+        <v>2.667296</v>
       </c>
       <c r="N42">
-        <v>18.97776</v>
+        <v>18.912704</v>
       </c>
       <c r="O42">
-        <v>4.744440000000001</v>
+        <v>4.728176</v>
       </c>
       <c r="P42">
-        <v>14.23332</v>
+        <v>14.184528</v>
       </c>
       <c r="Q42">
-        <v>16.45332</v>
+        <v>16.404528</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1269207734582489</v>
+        <v>0.1280665470946648</v>
       </c>
       <c r="T42">
-        <v>1.625957200287253</v>
+        <v>1.648922697466451</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.292855386128874</v>
+        <v>8.090590620613536</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09201051278585225</v>
+        <v>0.09181856149675517</v>
       </c>
       <c r="C43">
-        <v>82.81647873698481</v>
+        <v>82.10340716348125</v>
       </c>
       <c r="D43">
-        <v>120.5724787369848</v>
+        <v>121.0754071634813</v>
       </c>
       <c r="E43">
-        <v>18.256</v>
+        <v>19.472</v>
       </c>
       <c r="F43">
-        <v>49.856</v>
+        <v>51.072</v>
       </c>
       <c r="G43">
         <v>12.1</v>
@@ -4941,28 +4941,28 @@
         <v>21.58</v>
       </c>
       <c r="M43">
-        <v>2.667296</v>
+        <v>2.732352</v>
       </c>
       <c r="N43">
-        <v>18.912704</v>
+        <v>18.847648</v>
       </c>
       <c r="O43">
-        <v>4.728176</v>
+        <v>4.711912000000001</v>
       </c>
       <c r="P43">
-        <v>14.184528</v>
+        <v>14.135736</v>
       </c>
       <c r="Q43">
-        <v>16.404528</v>
+        <v>16.355736</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1280665470946648</v>
+        <v>0.1292518301668193</v>
       </c>
       <c r="T43">
-        <v>1.648922697466451</v>
+        <v>1.672680108341484</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.090590620613536</v>
+        <v>7.897957510598928</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09181856149675519</v>
+        <v>0.09162661020765808</v>
       </c>
       <c r="C44">
-        <v>82.10340716348122</v>
+        <v>81.39454876478395</v>
       </c>
       <c r="D44">
-        <v>121.0754071634812</v>
+        <v>121.582548764784</v>
       </c>
       <c r="E44">
-        <v>19.472</v>
+        <v>20.688</v>
       </c>
       <c r="F44">
-        <v>51.072</v>
+        <v>52.288</v>
       </c>
       <c r="G44">
         <v>12.1</v>
@@ -5023,28 +5023,28 @@
         <v>21.58</v>
       </c>
       <c r="M44">
-        <v>2.732352</v>
+        <v>2.797408</v>
       </c>
       <c r="N44">
-        <v>18.847648</v>
+        <v>18.782592</v>
       </c>
       <c r="O44">
-        <v>4.711912000000001</v>
+        <v>4.695648</v>
       </c>
       <c r="P44">
-        <v>14.135736</v>
+        <v>14.086944</v>
       </c>
       <c r="Q44">
-        <v>16.355736</v>
+        <v>16.306944</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1292518301668193</v>
+        <v>0.1304787021186984</v>
       </c>
       <c r="T44">
-        <v>1.672680108341484</v>
+        <v>1.697271112580553</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.897957510598929</v>
+        <v>7.714284080119883</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09162661020765808</v>
+        <v>0.09169865891856102</v>
       </c>
       <c r="C45">
-        <v>81.39454876478395</v>
+        <v>79.98769643678153</v>
       </c>
       <c r="D45">
-        <v>121.582548764784</v>
+        <v>121.3916964367815</v>
       </c>
       <c r="E45">
-        <v>20.688</v>
+        <v>21.904</v>
       </c>
       <c r="F45">
-        <v>52.288</v>
+        <v>53.504</v>
       </c>
       <c r="G45">
         <v>12.1</v>
@@ -5105,45 +5105,45 @@
         <v>21.58</v>
       </c>
       <c r="M45">
-        <v>2.797408</v>
+        <v>2.9052672</v>
       </c>
       <c r="N45">
-        <v>18.782592</v>
+        <v>18.6747328</v>
       </c>
       <c r="O45">
-        <v>4.695648</v>
+        <v>4.6686832</v>
       </c>
       <c r="P45">
-        <v>14.086944</v>
+        <v>14.0060496</v>
       </c>
       <c r="Q45">
-        <v>16.306944</v>
+        <v>16.2260496</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1304787021186984</v>
+        <v>0.1317493909260018</v>
       </c>
       <c r="T45">
-        <v>1.697271112580553</v>
+        <v>1.722740366971018</v>
       </c>
       <c r="U45">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y45">
-        <v>7.714284080119883</v>
+        <v>7.427888216271468</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09169865891856102</v>
+        <v>0.09151270762946392</v>
       </c>
       <c r="C46">
-        <v>79.98769643678153</v>
+        <v>79.26549659889562</v>
       </c>
       <c r="D46">
-        <v>121.3916964367815</v>
+        <v>121.8854965988956</v>
       </c>
       <c r="E46">
-        <v>21.904</v>
+        <v>23.12</v>
       </c>
       <c r="F46">
-        <v>53.504</v>
+        <v>54.72</v>
       </c>
       <c r="G46">
         <v>12.1</v>
@@ -5187,28 +5187,28 @@
         <v>21.58</v>
       </c>
       <c r="M46">
-        <v>2.9052672</v>
+        <v>2.971296</v>
       </c>
       <c r="N46">
-        <v>18.6747328</v>
+        <v>18.608704</v>
       </c>
       <c r="O46">
-        <v>4.6686832</v>
+        <v>4.652176000000001</v>
       </c>
       <c r="P46">
-        <v>14.0060496</v>
+        <v>13.956528</v>
       </c>
       <c r="Q46">
-        <v>16.2260496</v>
+        <v>16.176528</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1317493909260018</v>
+        <v>0.1330662865990253</v>
       </c>
       <c r="T46">
-        <v>1.722740366971018</v>
+        <v>1.74913577606659</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.427888216271468</v>
+        <v>7.262824033687657</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09151270762946392</v>
+        <v>0.09132675634036685</v>
       </c>
       <c r="C47">
-        <v>79.26549659889562</v>
+        <v>78.54733055494015</v>
       </c>
       <c r="D47">
-        <v>121.8854965988956</v>
+        <v>122.3833305549401</v>
       </c>
       <c r="E47">
-        <v>23.12</v>
+        <v>24.336</v>
       </c>
       <c r="F47">
-        <v>54.72</v>
+        <v>55.936</v>
       </c>
       <c r="G47">
         <v>12.1</v>
@@ -5269,28 +5269,28 @@
         <v>21.58</v>
       </c>
       <c r="M47">
-        <v>2.971296</v>
+        <v>3.0373248</v>
       </c>
       <c r="N47">
-        <v>18.608704</v>
+        <v>18.5426752</v>
       </c>
       <c r="O47">
-        <v>4.652176000000001</v>
+        <v>4.6356688</v>
       </c>
       <c r="P47">
-        <v>13.956528</v>
+        <v>13.9070064</v>
       </c>
       <c r="Q47">
-        <v>16.176528</v>
+        <v>16.1270064</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1330662865990253</v>
+        <v>0.1344319561858645</v>
       </c>
       <c r="T47">
-        <v>1.74913577606659</v>
+        <v>1.776508792906442</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.262824033687657</v>
+        <v>7.104936554694447</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09132675634036685</v>
+        <v>0.09114080505126977</v>
       </c>
       <c r="C48">
-        <v>78.54733055494015</v>
+        <v>77.83324793499004</v>
       </c>
       <c r="D48">
-        <v>122.3833305549401</v>
+        <v>122.88524793499</v>
       </c>
       <c r="E48">
-        <v>24.336</v>
+        <v>25.552</v>
       </c>
       <c r="F48">
-        <v>55.936</v>
+        <v>57.152</v>
       </c>
       <c r="G48">
         <v>12.1</v>
@@ -5351,28 +5351,28 @@
         <v>21.58</v>
       </c>
       <c r="M48">
-        <v>3.0373248</v>
+        <v>3.1033536</v>
       </c>
       <c r="N48">
-        <v>18.5426752</v>
+        <v>18.4766464</v>
       </c>
       <c r="O48">
-        <v>4.6356688</v>
+        <v>4.6191616</v>
       </c>
       <c r="P48">
-        <v>13.9070064</v>
+        <v>13.8574848</v>
       </c>
       <c r="Q48">
-        <v>16.1270064</v>
+        <v>16.0774848</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1344319561858645</v>
+        <v>0.1358491604740939</v>
       </c>
       <c r="T48">
-        <v>1.776508792906442</v>
+        <v>1.804914753777988</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.104936554694447</v>
+        <v>6.953767691828607</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09114080505126977</v>
+        <v>0.09095485376217269</v>
       </c>
       <c r="C49">
-        <v>77.83324793499004</v>
+        <v>77.12329918664241</v>
       </c>
       <c r="D49">
-        <v>122.88524793499</v>
+        <v>123.3912991866424</v>
       </c>
       <c r="E49">
-        <v>25.552</v>
+        <v>26.768</v>
       </c>
       <c r="F49">
-        <v>57.152</v>
+        <v>58.368</v>
       </c>
       <c r="G49">
         <v>12.1</v>
@@ -5433,28 +5433,28 @@
         <v>21.58</v>
       </c>
       <c r="M49">
-        <v>3.1033536</v>
+        <v>3.1693824</v>
       </c>
       <c r="N49">
-        <v>18.4766464</v>
+        <v>18.4106176</v>
       </c>
       <c r="O49">
-        <v>4.6191616</v>
+        <v>4.6026544</v>
       </c>
       <c r="P49">
-        <v>13.8574848</v>
+        <v>13.8079632</v>
       </c>
       <c r="Q49">
-        <v>16.0774848</v>
+        <v>16.0279632</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1358491604740939</v>
+        <v>0.1373208726195629</v>
       </c>
       <c r="T49">
-        <v>1.804914753777988</v>
+        <v>1.834413251606131</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.953767691828607</v>
+        <v>6.808897531582178</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09095485376217269</v>
+        <v>0.09076890247307559</v>
       </c>
       <c r="C50">
-        <v>77.12329918664241</v>
+        <v>76.41753559191955</v>
       </c>
       <c r="D50">
-        <v>123.3912991866424</v>
+        <v>123.9015355919195</v>
       </c>
       <c r="E50">
-        <v>26.768</v>
+        <v>27.984</v>
       </c>
       <c r="F50">
-        <v>58.36799999999999</v>
+        <v>59.584</v>
       </c>
       <c r="G50">
         <v>12.1</v>
@@ -5515,28 +5515,28 @@
         <v>21.58</v>
       </c>
       <c r="M50">
-        <v>3.1693824</v>
+        <v>3.2354112</v>
       </c>
       <c r="N50">
-        <v>18.4106176</v>
+        <v>18.3445888</v>
       </c>
       <c r="O50">
-        <v>4.6026544</v>
+        <v>4.586147200000001</v>
       </c>
       <c r="P50">
-        <v>13.8079632</v>
+        <v>13.7584416</v>
       </c>
       <c r="Q50">
-        <v>16.0279632</v>
+        <v>15.9784416</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1373208726195629</v>
+        <v>0.1388502989668149</v>
       </c>
       <c r="T50">
-        <v>1.834413251606131</v>
+        <v>1.865068553270672</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.808897531582179</v>
+        <v>6.669940439100911</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09076890247307559</v>
+        <v>0.09058295118397852</v>
       </c>
       <c r="C51">
-        <v>76.41753559191955</v>
+        <v>75.71600928459274</v>
       </c>
       <c r="D51">
-        <v>123.9015355919195</v>
+        <v>124.4160092845927</v>
       </c>
       <c r="E51">
-        <v>27.984</v>
+        <v>29.2</v>
       </c>
       <c r="F51">
-        <v>59.584</v>
+        <v>60.8</v>
       </c>
       <c r="G51">
         <v>12.1</v>
@@ -5597,28 +5597,28 @@
         <v>21.58</v>
       </c>
       <c r="M51">
-        <v>3.2354112</v>
+        <v>3.30144</v>
       </c>
       <c r="N51">
-        <v>18.3445888</v>
+        <v>18.27856</v>
       </c>
       <c r="O51">
-        <v>4.586147200000001</v>
+        <v>4.569640000000001</v>
       </c>
       <c r="P51">
-        <v>13.7584416</v>
+        <v>13.70892</v>
       </c>
       <c r="Q51">
-        <v>15.9784416</v>
+        <v>15.92892</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1388502989668149</v>
+        <v>0.140440902367957</v>
       </c>
       <c r="T51">
-        <v>1.865068553270672</v>
+        <v>1.896950067001795</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.669940439100911</v>
+        <v>6.536541630318892</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09058295118397852</v>
+        <v>0.09039699989488144</v>
       </c>
       <c r="C52">
-        <v>75.71600928459274</v>
+        <v>75.01877326793951</v>
       </c>
       <c r="D52">
-        <v>124.4160092845927</v>
+        <v>124.9347732679395</v>
       </c>
       <c r="E52">
-        <v>29.2</v>
+        <v>30.416</v>
       </c>
       <c r="F52">
-        <v>60.8</v>
+        <v>62.016</v>
       </c>
       <c r="G52">
         <v>12.1</v>
@@ -5679,28 +5679,28 @@
         <v>21.58</v>
       </c>
       <c r="M52">
-        <v>3.30144</v>
+        <v>3.3674688</v>
       </c>
       <c r="N52">
-        <v>18.27856</v>
+        <v>18.2125312</v>
       </c>
       <c r="O52">
-        <v>4.569640000000001</v>
+        <v>4.5531328</v>
       </c>
       <c r="P52">
-        <v>13.70892</v>
+        <v>13.6593984</v>
       </c>
       <c r="Q52">
-        <v>15.92892</v>
+        <v>15.8793984</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.140440902367957</v>
+        <v>0.1420964283569009</v>
       </c>
       <c r="T52">
-        <v>1.896950067001795</v>
+        <v>1.930132867007657</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.536541630318892</v>
+        <v>6.408374147371462</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09039699989488144</v>
+        <v>0.09021104860578436</v>
       </c>
       <c r="C53">
-        <v>75.01877326793951</v>
+        <v>74.32588143294689</v>
       </c>
       <c r="D53">
-        <v>124.9347732679395</v>
+        <v>125.4578814329469</v>
       </c>
       <c r="E53">
-        <v>30.416</v>
+        <v>31.632</v>
       </c>
       <c r="F53">
-        <v>62.016</v>
+        <v>63.232</v>
       </c>
       <c r="G53">
         <v>12.1</v>
@@ -5761,28 +5761,28 @@
         <v>21.58</v>
       </c>
       <c r="M53">
-        <v>3.3674688</v>
+        <v>3.4334976</v>
       </c>
       <c r="N53">
-        <v>18.2125312</v>
+        <v>18.1465024</v>
       </c>
       <c r="O53">
-        <v>4.5531328</v>
+        <v>4.536625600000001</v>
       </c>
       <c r="P53">
-        <v>13.6593984</v>
+        <v>13.6098768</v>
       </c>
       <c r="Q53">
-        <v>15.8793984</v>
+        <v>15.8298768</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1420964283569009</v>
+        <v>0.1438209345953841</v>
       </c>
       <c r="T53">
-        <v>1.930132867007657</v>
+        <v>1.96469828368043</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.408374147371462</v>
+        <v>6.285136182998935</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09021104860578436</v>
+        <v>0.09002509731668727</v>
       </c>
       <c r="C54">
-        <v>74.32588143294689</v>
+        <v>73.63738857697398</v>
       </c>
       <c r="D54">
-        <v>125.4578814329469</v>
+        <v>125.985388576974</v>
       </c>
       <c r="E54">
-        <v>31.632</v>
+        <v>32.848</v>
       </c>
       <c r="F54">
-        <v>63.232</v>
+        <v>64.44799999999999</v>
       </c>
       <c r="G54">
         <v>12.1</v>
@@ -5843,28 +5843,28 @@
         <v>21.58</v>
       </c>
       <c r="M54">
-        <v>3.4334976</v>
+        <v>3.4995264</v>
       </c>
       <c r="N54">
-        <v>18.1465024</v>
+        <v>18.0804736</v>
       </c>
       <c r="O54">
-        <v>4.536625600000001</v>
+        <v>4.5201184</v>
       </c>
       <c r="P54">
-        <v>13.6098768</v>
+        <v>13.5603552</v>
       </c>
       <c r="Q54">
-        <v>15.8298768</v>
+        <v>15.7803552</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1438209345953841</v>
+        <v>0.145618824078058</v>
       </c>
       <c r="T54">
-        <v>1.96469828368043</v>
+        <v>2.00073456914779</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.285136182998935</v>
+        <v>6.166548707848011</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09002509731668727</v>
+        <v>0.09024414602759019</v>
       </c>
       <c r="C55">
-        <v>73.63738857697398</v>
+        <v>71.80045332617046</v>
       </c>
       <c r="D55">
-        <v>125.985388576974</v>
+        <v>125.3644533261704</v>
       </c>
       <c r="E55">
-        <v>32.848</v>
+        <v>34.06400000000001</v>
       </c>
       <c r="F55">
-        <v>64.44799999999999</v>
+        <v>65.664</v>
       </c>
       <c r="G55">
         <v>12.1</v>
@@ -5925,45 +5925,45 @@
         <v>21.58</v>
       </c>
       <c r="M55">
-        <v>3.4995264</v>
+        <v>3.6312192</v>
       </c>
       <c r="N55">
-        <v>18.0804736</v>
+        <v>17.9487808</v>
       </c>
       <c r="O55">
-        <v>4.5201184</v>
+        <v>4.4871952</v>
       </c>
       <c r="P55">
-        <v>13.5603552</v>
+        <v>13.4615856</v>
       </c>
       <c r="Q55">
-        <v>15.7803552</v>
+        <v>15.6815856</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.145618824078058</v>
+        <v>0.1474948826686743</v>
       </c>
       <c r="T55">
-        <v>2.00073456914779</v>
+        <v>2.038337649635469</v>
       </c>
       <c r="U55">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>6.166548707848011</v>
+        <v>5.942907550169376</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09024414602759019</v>
+        <v>0.09006569473849312</v>
       </c>
       <c r="C56">
-        <v>71.80045332617046</v>
+        <v>71.08984352585372</v>
       </c>
       <c r="D56">
-        <v>125.3644533261704</v>
+        <v>125.8698435258537</v>
       </c>
       <c r="E56">
-        <v>34.06400000000001</v>
+        <v>35.28</v>
       </c>
       <c r="F56">
-        <v>65.664</v>
+        <v>66.88</v>
       </c>
       <c r="G56">
         <v>12.1</v>
@@ -6007,28 +6007,28 @@
         <v>21.58</v>
       </c>
       <c r="M56">
-        <v>3.6312192</v>
+        <v>3.698464</v>
       </c>
       <c r="N56">
-        <v>17.9487808</v>
+        <v>17.881536</v>
       </c>
       <c r="O56">
-        <v>4.4871952</v>
+        <v>4.470384</v>
       </c>
       <c r="P56">
-        <v>13.4615856</v>
+        <v>13.411152</v>
       </c>
       <c r="Q56">
-        <v>15.6815856</v>
+        <v>15.631152</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1474948826686743</v>
+        <v>0.1494543216410958</v>
       </c>
       <c r="T56">
-        <v>2.038337649635469</v>
+        <v>2.077611978144823</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.942907550169376</v>
+        <v>5.834854685620842</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09006569473849312</v>
+        <v>0.08988724344939603</v>
       </c>
       <c r="C57">
-        <v>71.08984352585372</v>
+        <v>70.38332504654392</v>
       </c>
       <c r="D57">
-        <v>125.8698435258537</v>
+        <v>126.3793250465439</v>
       </c>
       <c r="E57">
-        <v>35.28</v>
+        <v>36.49600000000001</v>
       </c>
       <c r="F57">
-        <v>66.88</v>
+        <v>68.096</v>
       </c>
       <c r="G57">
         <v>12.1</v>
@@ -6089,28 +6089,28 @@
         <v>21.58</v>
       </c>
       <c r="M57">
-        <v>3.698464</v>
+        <v>3.765708800000001</v>
       </c>
       <c r="N57">
-        <v>17.881536</v>
+        <v>17.8142912</v>
       </c>
       <c r="O57">
-        <v>4.470384</v>
+        <v>4.4535728</v>
       </c>
       <c r="P57">
-        <v>13.411152</v>
+        <v>13.3607184</v>
       </c>
       <c r="Q57">
-        <v>15.631152</v>
+        <v>15.5807184</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1494543216410958</v>
+        <v>0.1515028260213546</v>
       </c>
       <c r="T57">
-        <v>2.077611978144823</v>
+        <v>2.118671503404602</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.834854685620842</v>
+        <v>5.73066085194904</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08988724344939603</v>
+        <v>0.08970879216029895</v>
       </c>
       <c r="C58">
-        <v>70.38332504654392</v>
+        <v>69.68094777129208</v>
       </c>
       <c r="D58">
-        <v>126.3793250465439</v>
+        <v>126.8929477712921</v>
       </c>
       <c r="E58">
-        <v>36.49600000000001</v>
+        <v>37.712</v>
       </c>
       <c r="F58">
-        <v>68.096</v>
+        <v>69.312</v>
       </c>
       <c r="G58">
         <v>12.1</v>
@@ -6171,28 +6171,28 @@
         <v>21.58</v>
       </c>
       <c r="M58">
-        <v>3.765708800000001</v>
+        <v>3.8329536</v>
       </c>
       <c r="N58">
-        <v>17.8142912</v>
+        <v>17.7470464</v>
       </c>
       <c r="O58">
-        <v>4.4535728</v>
+        <v>4.436761600000001</v>
       </c>
       <c r="P58">
-        <v>13.3607184</v>
+        <v>13.3102848</v>
       </c>
       <c r="Q58">
-        <v>15.5807184</v>
+        <v>15.5302848</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1515028260213546</v>
+        <v>0.1536466096751138</v>
       </c>
       <c r="T58">
-        <v>2.118671503404602</v>
+        <v>2.161640774025301</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.73066085194904</v>
+        <v>5.630122942265724</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08970879216029895</v>
+        <v>0.08953034087120187</v>
       </c>
       <c r="C59">
-        <v>69.68094777129208</v>
+        <v>68.98276239738449</v>
       </c>
       <c r="D59">
-        <v>126.8929477712921</v>
+        <v>127.4107623973845</v>
       </c>
       <c r="E59">
-        <v>37.712</v>
+        <v>38.92800000000001</v>
       </c>
       <c r="F59">
-        <v>69.312</v>
+        <v>70.52800000000001</v>
       </c>
       <c r="G59">
         <v>12.1</v>
@@ -6253,28 +6253,28 @@
         <v>21.58</v>
       </c>
       <c r="M59">
-        <v>3.8329536</v>
+        <v>3.9001984</v>
       </c>
       <c r="N59">
-        <v>17.7470464</v>
+        <v>17.6798016</v>
       </c>
       <c r="O59">
-        <v>4.436761600000001</v>
+        <v>4.4199504</v>
       </c>
       <c r="P59">
-        <v>13.3102848</v>
+        <v>13.2598512</v>
       </c>
       <c r="Q59">
-        <v>15.5302848</v>
+        <v>15.4798512</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1536466096751138</v>
+        <v>0.1558924782647664</v>
       </c>
       <c r="T59">
-        <v>2.161640774025301</v>
+        <v>2.206656200389843</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.630122942265724</v>
+        <v>5.533051857054247</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08953034087120186</v>
+        <v>0.08935188958210478</v>
       </c>
       <c r="C60">
-        <v>68.98276239738456</v>
+        <v>68.28882045302393</v>
       </c>
       <c r="D60">
-        <v>127.4107623973845</v>
+        <v>127.9328204530239</v>
       </c>
       <c r="E60">
-        <v>38.928</v>
+        <v>40.14400000000001</v>
       </c>
       <c r="F60">
-        <v>70.52799999999999</v>
+        <v>71.744</v>
       </c>
       <c r="G60">
         <v>12.1</v>
@@ -6335,28 +6335,28 @@
         <v>21.58</v>
       </c>
       <c r="M60">
-        <v>3.9001984</v>
+        <v>3.9674432</v>
       </c>
       <c r="N60">
-        <v>17.6798016</v>
+        <v>17.6125568</v>
       </c>
       <c r="O60">
-        <v>4.4199504</v>
+        <v>4.4031392</v>
       </c>
       <c r="P60">
-        <v>13.2598512</v>
+        <v>13.2094176</v>
       </c>
       <c r="Q60">
-        <v>15.4798512</v>
+        <v>15.4294176</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1558924782647663</v>
+        <v>0.1582479014197678</v>
       </c>
       <c r="T60">
-        <v>2.206656200389843</v>
+        <v>2.253867501211191</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.533051857054247</v>
+        <v>5.439271317104175</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08935188958210478</v>
+        <v>0.08917343829300772</v>
       </c>
       <c r="C61">
-        <v>68.28882045302393</v>
+        <v>67.59917431442265</v>
       </c>
       <c r="D61">
-        <v>127.9328204530239</v>
+        <v>128.4591743144227</v>
       </c>
       <c r="E61">
-        <v>40.14400000000001</v>
+        <v>41.36</v>
       </c>
       <c r="F61">
-        <v>71.744</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="G61">
         <v>12.1</v>
@@ -6417,28 +6417,28 @@
         <v>21.58</v>
       </c>
       <c r="M61">
-        <v>3.9674432</v>
+        <v>4.034688</v>
       </c>
       <c r="N61">
-        <v>17.6125568</v>
+        <v>17.545312</v>
       </c>
       <c r="O61">
-        <v>4.4031392</v>
+        <v>4.386328000000001</v>
       </c>
       <c r="P61">
-        <v>13.2094176</v>
+        <v>13.158984</v>
       </c>
       <c r="Q61">
-        <v>15.4294176</v>
+        <v>15.378984</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1582479014197678</v>
+        <v>0.1607210957325193</v>
       </c>
       <c r="T61">
-        <v>2.253867501211191</v>
+        <v>2.303439367073608</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.439271317104175</v>
+        <v>5.348616795152439</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08917343829300772</v>
+        <v>0.08899498700391063</v>
       </c>
       <c r="C62">
-        <v>67.59917431442265</v>
+        <v>66.91387722331997</v>
       </c>
       <c r="D62">
-        <v>128.4591743144227</v>
+        <v>128.98987722332</v>
       </c>
       <c r="E62">
-        <v>41.36</v>
+        <v>42.57600000000001</v>
       </c>
       <c r="F62">
-        <v>72.95999999999999</v>
+        <v>74.176</v>
       </c>
       <c r="G62">
         <v>12.1</v>
@@ -6499,28 +6499,28 @@
         <v>21.58</v>
       </c>
       <c r="M62">
-        <v>4.034688</v>
+        <v>4.1019328</v>
       </c>
       <c r="N62">
-        <v>17.545312</v>
+        <v>17.4780672</v>
       </c>
       <c r="O62">
-        <v>4.386328000000001</v>
+        <v>4.3695168</v>
       </c>
       <c r="P62">
-        <v>13.158984</v>
+        <v>13.1085504</v>
       </c>
       <c r="Q62">
-        <v>15.378984</v>
+        <v>15.3285504</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1607210957325193</v>
+        <v>0.1633211205228478</v>
       </c>
       <c r="T62">
-        <v>2.303439367073608</v>
+        <v>2.355553379903328</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.348616795152439</v>
+        <v>5.260934552608956</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08899498700391063</v>
+        <v>0.08881653571481354</v>
       </c>
       <c r="C63">
-        <v>66.91387722331997</v>
+        <v>66.23298330493432</v>
       </c>
       <c r="D63">
-        <v>128.98987722332</v>
+        <v>129.5249833049343</v>
       </c>
       <c r="E63">
-        <v>42.57600000000001</v>
+        <v>43.792</v>
       </c>
       <c r="F63">
-        <v>74.176</v>
+        <v>75.392</v>
       </c>
       <c r="G63">
         <v>12.1</v>
@@ -6581,28 +6581,28 @@
         <v>21.58</v>
       </c>
       <c r="M63">
-        <v>4.1019328</v>
+        <v>4.1691776</v>
       </c>
       <c r="N63">
-        <v>17.4780672</v>
+        <v>17.4108224</v>
       </c>
       <c r="O63">
-        <v>4.3695168</v>
+        <v>4.3527056</v>
       </c>
       <c r="P63">
-        <v>13.1085504</v>
+        <v>13.0581168</v>
       </c>
       <c r="Q63">
-        <v>15.3285504</v>
+        <v>15.2781168</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1633211205228478</v>
+        <v>0.1660579887231935</v>
       </c>
       <c r="T63">
-        <v>2.355553379903328</v>
+        <v>2.410410235513559</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.260934552608956</v>
+        <v>5.176080769502359</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08881653571481354</v>
+        <v>0.08863808442571647</v>
       </c>
       <c r="C64">
-        <v>66.23298330493432</v>
+        <v>65.55654758636534</v>
       </c>
       <c r="D64">
-        <v>129.5249833049343</v>
+        <v>130.0645475863653</v>
       </c>
       <c r="E64">
-        <v>43.792</v>
+        <v>45.008</v>
       </c>
       <c r="F64">
-        <v>75.392</v>
+        <v>76.60799999999999</v>
       </c>
       <c r="G64">
         <v>12.1</v>
@@ -6663,28 +6663,28 @@
         <v>21.58</v>
       </c>
       <c r="M64">
-        <v>4.1691776</v>
+        <v>4.236422399999999</v>
       </c>
       <c r="N64">
-        <v>17.4108224</v>
+        <v>17.3435776</v>
       </c>
       <c r="O64">
-        <v>4.3527056</v>
+        <v>4.335894400000001</v>
       </c>
       <c r="P64">
-        <v>13.0581168</v>
+        <v>13.0076832</v>
       </c>
       <c r="Q64">
-        <v>15.2781168</v>
+        <v>15.2276832</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1660579887231935</v>
+        <v>0.1689427957451796</v>
       </c>
       <c r="T64">
-        <v>2.410410235513559</v>
+        <v>2.468232326562181</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.176080769502359</v>
+        <v>5.093920757288037</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08863808442571647</v>
+        <v>0.08845963313661938</v>
       </c>
       <c r="C65">
-        <v>65.55654758636534</v>
+        <v>64.88462601545741</v>
       </c>
       <c r="D65">
-        <v>130.0645475863653</v>
+        <v>130.6086260154574</v>
       </c>
       <c r="E65">
-        <v>45.008</v>
+        <v>46.224</v>
       </c>
       <c r="F65">
-        <v>76.60799999999999</v>
+        <v>77.824</v>
       </c>
       <c r="G65">
         <v>12.1</v>
@@ -6745,28 +6745,28 @@
         <v>21.58</v>
       </c>
       <c r="M65">
-        <v>4.236422399999999</v>
+        <v>4.3036672</v>
       </c>
       <c r="N65">
-        <v>17.3435776</v>
+        <v>17.2763328</v>
       </c>
       <c r="O65">
-        <v>4.335894400000001</v>
+        <v>4.319083200000001</v>
       </c>
       <c r="P65">
-        <v>13.0076832</v>
+        <v>12.9572496</v>
       </c>
       <c r="Q65">
-        <v>15.2276832</v>
+        <v>15.1772496</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1689427957451796</v>
+        <v>0.1719878698239427</v>
       </c>
       <c r="T65">
-        <v>2.468232326562181</v>
+        <v>2.529266756002393</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.093920757288037</v>
+        <v>5.014328245455411</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08845963313661938</v>
+        <v>0.0882811818475223</v>
       </c>
       <c r="C66">
-        <v>64.88462601545741</v>
+        <v>64.21727548013834</v>
       </c>
       <c r="D66">
-        <v>130.6086260154574</v>
+        <v>131.1572754801383</v>
       </c>
       <c r="E66">
-        <v>46.224</v>
+        <v>47.44</v>
       </c>
       <c r="F66">
-        <v>77.824</v>
+        <v>79.03999999999999</v>
       </c>
       <c r="G66">
         <v>12.1</v>
@@ -6827,28 +6827,28 @@
         <v>21.58</v>
       </c>
       <c r="M66">
-        <v>4.3036672</v>
+        <v>4.370912</v>
       </c>
       <c r="N66">
-        <v>17.2763328</v>
+        <v>17.209088</v>
       </c>
       <c r="O66">
-        <v>4.319083200000001</v>
+        <v>4.302272</v>
       </c>
       <c r="P66">
-        <v>12.9572496</v>
+        <v>12.906816</v>
       </c>
       <c r="Q66">
-        <v>15.1772496</v>
+        <v>15.126816</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1719878698239427</v>
+        <v>0.175206948135778</v>
       </c>
       <c r="T66">
-        <v>2.529266756002393</v>
+        <v>2.593788867124903</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.014328245455411</v>
+        <v>4.937184733986866</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0882811818475223</v>
+        <v>0.08810273055842521</v>
       </c>
       <c r="C67">
-        <v>64.21727548013834</v>
+        <v>63.55455382824798</v>
       </c>
       <c r="D67">
-        <v>131.1572754801383</v>
+        <v>131.710553828248</v>
       </c>
       <c r="E67">
-        <v>47.44</v>
+        <v>48.65600000000001</v>
       </c>
       <c r="F67">
-        <v>79.03999999999999</v>
+        <v>80.256</v>
       </c>
       <c r="G67">
         <v>12.1</v>
@@ -6909,28 +6909,28 @@
         <v>21.58</v>
       </c>
       <c r="M67">
-        <v>4.370912</v>
+        <v>4.4381568</v>
       </c>
       <c r="N67">
-        <v>17.209088</v>
+        <v>17.1418432</v>
       </c>
       <c r="O67">
-        <v>4.302272</v>
+        <v>4.285460800000001</v>
       </c>
       <c r="P67">
-        <v>12.906816</v>
+        <v>12.8563824</v>
       </c>
       <c r="Q67">
-        <v>15.126816</v>
+        <v>15.0763824</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.175206948135778</v>
+        <v>0.1786153839953683</v>
       </c>
       <c r="T67">
-        <v>2.593788867124903</v>
+        <v>2.662106396548737</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.937184733986866</v>
+        <v>4.862378904684036</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08810273055842521</v>
+        <v>0.08792427926932814</v>
       </c>
       <c r="C68">
-        <v>63.55455382824798</v>
+        <v>62.89651988787038</v>
       </c>
       <c r="D68">
-        <v>131.710553828248</v>
+        <v>132.2685198878704</v>
       </c>
       <c r="E68">
-        <v>48.65600000000001</v>
+        <v>49.872</v>
       </c>
       <c r="F68">
-        <v>80.256</v>
+        <v>81.47199999999999</v>
       </c>
       <c r="G68">
         <v>12.1</v>
@@ -6991,28 +6991,28 @@
         <v>21.58</v>
       </c>
       <c r="M68">
-        <v>4.4381568</v>
+        <v>4.5054016</v>
       </c>
       <c r="N68">
-        <v>17.1418432</v>
+        <v>17.0745984</v>
       </c>
       <c r="O68">
-        <v>4.285460800000001</v>
+        <v>4.268649600000001</v>
       </c>
       <c r="P68">
-        <v>12.8563824</v>
+        <v>12.8059488</v>
       </c>
       <c r="Q68">
-        <v>15.0763824</v>
+        <v>15.0259488</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1786153839953683</v>
+        <v>0.1822303917252368</v>
       </c>
       <c r="T68">
-        <v>2.662106396548737</v>
+        <v>2.734564382301289</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.862378904684036</v>
+        <v>4.78980608521114</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08792427926932814</v>
+        <v>0.08774582798023106</v>
       </c>
       <c r="C69">
-        <v>62.89651988787038</v>
+        <v>62.24323348818545</v>
       </c>
       <c r="D69">
-        <v>132.2685198878704</v>
+        <v>132.8312334881855</v>
       </c>
       <c r="E69">
-        <v>49.872</v>
+        <v>51.08800000000001</v>
       </c>
       <c r="F69">
-        <v>81.47199999999999</v>
+        <v>82.688</v>
       </c>
       <c r="G69">
         <v>12.1</v>
@@ -7073,28 +7073,28 @@
         <v>21.58</v>
       </c>
       <c r="M69">
-        <v>4.5054016</v>
+        <v>4.5726464</v>
       </c>
       <c r="N69">
-        <v>17.0745984</v>
+        <v>17.0073536</v>
       </c>
       <c r="O69">
-        <v>4.268649600000001</v>
+        <v>4.2518384</v>
       </c>
       <c r="P69">
-        <v>12.8059488</v>
+        <v>12.7555152</v>
       </c>
       <c r="Q69">
-        <v>15.0259488</v>
+        <v>14.9755152</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1822303917252368</v>
+        <v>0.1860713374382221</v>
       </c>
       <c r="T69">
-        <v>2.734564382301289</v>
+        <v>2.811550992163375</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.78980608521114</v>
+        <v>4.719367760428622</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08774582798023106</v>
+        <v>0.08756737669113397</v>
       </c>
       <c r="C70">
-        <v>62.24323348818545</v>
+        <v>61.59475548085479</v>
       </c>
       <c r="D70">
-        <v>132.8312334881855</v>
+        <v>133.3987554808548</v>
       </c>
       <c r="E70">
-        <v>51.08800000000001</v>
+        <v>52.304</v>
       </c>
       <c r="F70">
-        <v>82.688</v>
+        <v>83.904</v>
       </c>
       <c r="G70">
         <v>12.1</v>
@@ -7155,28 +7155,28 @@
         <v>21.58</v>
       </c>
       <c r="M70">
-        <v>4.5726464</v>
+        <v>4.6398912</v>
       </c>
       <c r="N70">
-        <v>17.0073536</v>
+        <v>16.9401088</v>
       </c>
       <c r="O70">
-        <v>4.2518384</v>
+        <v>4.2350272</v>
       </c>
       <c r="P70">
-        <v>12.7555152</v>
+        <v>12.7050816</v>
       </c>
       <c r="Q70">
-        <v>14.9755152</v>
+        <v>14.9250816</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1860713374382221</v>
+        <v>0.1901600861004322</v>
       </c>
       <c r="T70">
-        <v>2.811550992163375</v>
+        <v>2.893504480081079</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.719367760428622</v>
+        <v>4.650971126219511</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08756737669113397</v>
+        <v>0.08738892540203688</v>
       </c>
       <c r="C71">
-        <v>61.59475548085479</v>
+        <v>60.95114776195808</v>
       </c>
       <c r="D71">
-        <v>133.3987554808548</v>
+        <v>133.9711477619581</v>
       </c>
       <c r="E71">
-        <v>52.304</v>
+        <v>53.52000000000001</v>
       </c>
       <c r="F71">
-        <v>83.904</v>
+        <v>85.12</v>
       </c>
       <c r="G71">
         <v>12.1</v>
@@ -7237,28 +7237,28 @@
         <v>21.58</v>
       </c>
       <c r="M71">
-        <v>4.6398912</v>
+        <v>4.707136</v>
       </c>
       <c r="N71">
-        <v>16.9401088</v>
+        <v>16.872864</v>
       </c>
       <c r="O71">
-        <v>4.2350272</v>
+        <v>4.218216</v>
       </c>
       <c r="P71">
-        <v>12.7050816</v>
+        <v>12.654648</v>
       </c>
       <c r="Q71">
-        <v>14.9250816</v>
+        <v>14.874648</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1901600861004322</v>
+        <v>0.1945214180067897</v>
       </c>
       <c r="T71">
-        <v>2.893504480081079</v>
+        <v>2.980921533859963</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.650971126219511</v>
+        <v>4.584528681559233</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08738892540203688</v>
+        <v>0.08721047411293981</v>
       </c>
       <c r="C72">
-        <v>60.95114776195808</v>
+        <v>60.31247329449685</v>
       </c>
       <c r="D72">
-        <v>133.9711477619581</v>
+        <v>134.5484732944969</v>
       </c>
       <c r="E72">
-        <v>53.52000000000001</v>
+        <v>54.736</v>
       </c>
       <c r="F72">
-        <v>85.12</v>
+        <v>86.336</v>
       </c>
       <c r="G72">
         <v>12.1</v>
@@ -7319,28 +7319,28 @@
         <v>21.58</v>
       </c>
       <c r="M72">
-        <v>4.707136</v>
+        <v>4.7743808</v>
       </c>
       <c r="N72">
-        <v>16.872864</v>
+        <v>16.8056192</v>
       </c>
       <c r="O72">
-        <v>4.218216</v>
+        <v>4.201404800000001</v>
       </c>
       <c r="P72">
-        <v>12.654648</v>
+        <v>12.6042144</v>
       </c>
       <c r="Q72">
-        <v>14.874648</v>
+        <v>14.8242144</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1945214180067897</v>
+        <v>0.1991835314239304</v>
       </c>
       <c r="T72">
-        <v>2.980921533859963</v>
+        <v>3.074367349968427</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.584528681559233</v>
+        <v>4.519957855058399</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08721047411293982</v>
+        <v>0.08838202282384273</v>
       </c>
       <c r="C73">
-        <v>60.3124732944968</v>
+        <v>55.39467427254283</v>
       </c>
       <c r="D73">
-        <v>134.5484732944968</v>
+        <v>130.8466742725428</v>
       </c>
       <c r="E73">
-        <v>54.736</v>
+        <v>55.952</v>
       </c>
       <c r="F73">
-        <v>86.336</v>
+        <v>87.55199999999999</v>
       </c>
       <c r="G73">
         <v>12.1</v>
@@ -7401,45 +7401,45 @@
         <v>21.58</v>
       </c>
       <c r="M73">
-        <v>4.7743808</v>
+        <v>5.0605056</v>
       </c>
       <c r="N73">
-        <v>16.8056192</v>
+        <v>16.5194944</v>
       </c>
       <c r="O73">
-        <v>4.201404800000001</v>
+        <v>4.129873600000001</v>
       </c>
       <c r="P73">
-        <v>12.6042144</v>
+        <v>12.3896208</v>
       </c>
       <c r="Q73">
-        <v>14.8242144</v>
+        <v>14.6096208</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1991835314239304</v>
+        <v>0.2041786529422955</v>
       </c>
       <c r="T73">
-        <v>3.074367349968426</v>
+        <v>3.174487867227493</v>
       </c>
       <c r="U73">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.519957855058399</v>
+        <v>4.264396031890569</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08838202282384273</v>
+        <v>0.08822232153474566</v>
       </c>
       <c r="C74">
-        <v>55.39467427254283</v>
+        <v>54.67125416443477</v>
       </c>
       <c r="D74">
-        <v>130.8466742725428</v>
+        <v>131.3392541644348</v>
       </c>
       <c r="E74">
-        <v>55.952</v>
+        <v>57.16800000000001</v>
       </c>
       <c r="F74">
-        <v>87.55199999999999</v>
+        <v>88.768</v>
       </c>
       <c r="G74">
         <v>12.1</v>
@@ -7483,28 +7483,28 @@
         <v>21.58</v>
       </c>
       <c r="M74">
-        <v>5.0605056</v>
+        <v>5.1307904</v>
       </c>
       <c r="N74">
-        <v>16.5194944</v>
+        <v>16.4492096</v>
       </c>
       <c r="O74">
-        <v>4.129873600000001</v>
+        <v>4.112302400000001</v>
       </c>
       <c r="P74">
-        <v>12.3896208</v>
+        <v>12.3369072</v>
       </c>
       <c r="Q74">
-        <v>14.6096208</v>
+        <v>14.5569072</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2041786529422955</v>
+        <v>0.2095437834620209</v>
       </c>
       <c r="T74">
-        <v>3.174487867227493</v>
+        <v>3.282024719098343</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.264396031890569</v>
+        <v>4.205979647892068</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08822232153474566</v>
+        <v>0.08806262024564857</v>
       </c>
       <c r="C75">
-        <v>54.67125416443477</v>
+        <v>53.95155676179375</v>
       </c>
       <c r="D75">
-        <v>131.3392541644348</v>
+        <v>131.8355567617938</v>
       </c>
       <c r="E75">
-        <v>57.16800000000001</v>
+        <v>58.384</v>
       </c>
       <c r="F75">
-        <v>88.768</v>
+        <v>89.98399999999999</v>
       </c>
       <c r="G75">
         <v>12.1</v>
@@ -7565,28 +7565,28 @@
         <v>21.58</v>
       </c>
       <c r="M75">
-        <v>5.1307904</v>
+        <v>5.2010752</v>
       </c>
       <c r="N75">
-        <v>16.4492096</v>
+        <v>16.3789248</v>
       </c>
       <c r="O75">
-        <v>4.112302400000001</v>
+        <v>4.0947312</v>
       </c>
       <c r="P75">
-        <v>12.3369072</v>
+        <v>12.2841936</v>
       </c>
       <c r="Q75">
-        <v>14.5569072</v>
+        <v>14.5041936</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2095437834620209</v>
+        <v>0.2153216163294175</v>
       </c>
       <c r="T75">
-        <v>3.282024719098343</v>
+        <v>3.39783363649772</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.205979647892068</v>
+        <v>4.149142085082715</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08806262024564857</v>
+        <v>0.08790291895655149</v>
       </c>
       <c r="C76">
-        <v>53.95155676179375</v>
+        <v>53.23562442658954</v>
       </c>
       <c r="D76">
-        <v>131.8355567617938</v>
+        <v>132.3356244265895</v>
       </c>
       <c r="E76">
-        <v>58.384</v>
+        <v>59.59999999999999</v>
       </c>
       <c r="F76">
-        <v>89.98399999999999</v>
+        <v>91.19999999999999</v>
       </c>
       <c r="G76">
         <v>12.1</v>
@@ -7647,28 +7647,28 @@
         <v>21.58</v>
       </c>
       <c r="M76">
-        <v>5.2010752</v>
+        <v>5.27136</v>
       </c>
       <c r="N76">
-        <v>16.3789248</v>
+        <v>16.30864</v>
       </c>
       <c r="O76">
-        <v>4.0947312</v>
+        <v>4.077160000000001</v>
       </c>
       <c r="P76">
-        <v>12.2841936</v>
+        <v>12.23148</v>
       </c>
       <c r="Q76">
-        <v>14.5041936</v>
+        <v>14.45148</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2153216163294175</v>
+        <v>0.221561675826206</v>
       </c>
       <c r="T76">
-        <v>3.39783363649772</v>
+        <v>3.522907267289047</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.149142085082715</v>
+        <v>4.093820190614947</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08790291895655149</v>
+        <v>0.08774321766745441</v>
       </c>
       <c r="C77">
-        <v>53.23562442658954</v>
+        <v>52.52350016597498</v>
       </c>
       <c r="D77">
-        <v>132.3356244265895</v>
+        <v>132.839500165975</v>
       </c>
       <c r="E77">
-        <v>59.59999999999999</v>
+        <v>60.816</v>
       </c>
       <c r="F77">
-        <v>91.19999999999999</v>
+        <v>92.416</v>
       </c>
       <c r="G77">
         <v>12.1</v>
@@ -7729,28 +7729,28 @@
         <v>21.58</v>
       </c>
       <c r="M77">
-        <v>5.27136</v>
+        <v>5.3416448</v>
       </c>
       <c r="N77">
-        <v>16.30864</v>
+        <v>16.2383552</v>
       </c>
       <c r="O77">
-        <v>4.077160000000001</v>
+        <v>4.0595888</v>
       </c>
       <c r="P77">
-        <v>12.23148</v>
+        <v>12.1787664</v>
       </c>
       <c r="Q77">
-        <v>14.45148</v>
+        <v>14.3987664</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.221561675826206</v>
+        <v>0.22832174028106</v>
       </c>
       <c r="T77">
-        <v>3.522907267289047</v>
+        <v>3.658403700646318</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.093820190614947</v>
+        <v>4.039954135475275</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08774321766745441</v>
+        <v>0.08960476637835732</v>
       </c>
       <c r="C78">
-        <v>52.52350016597498</v>
+        <v>45.66228799533924</v>
       </c>
       <c r="D78">
-        <v>132.839500165975</v>
+        <v>127.1942879953392</v>
       </c>
       <c r="E78">
-        <v>60.816</v>
+        <v>62.032</v>
       </c>
       <c r="F78">
-        <v>92.416</v>
+        <v>93.63199999999999</v>
       </c>
       <c r="G78">
         <v>12.1</v>
@@ -7811,45 +7811,45 @@
         <v>21.58</v>
       </c>
       <c r="M78">
-        <v>5.3416448</v>
+        <v>5.7396416</v>
       </c>
       <c r="N78">
-        <v>16.2383552</v>
+        <v>15.8403584</v>
       </c>
       <c r="O78">
-        <v>4.0595888</v>
+        <v>3.960089600000001</v>
       </c>
       <c r="P78">
-        <v>12.1787664</v>
+        <v>11.8802688</v>
       </c>
       <c r="Q78">
-        <v>14.3987664</v>
+        <v>14.1002688</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.22832174028106</v>
+        <v>0.2356696364276405</v>
       </c>
       <c r="T78">
-        <v>3.658403700646318</v>
+        <v>3.805682432556396</v>
       </c>
       <c r="U78">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>4.039954135475275</v>
+        <v>3.759816640816041</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08960476637835732</v>
+        <v>0.08947131508926023</v>
       </c>
       <c r="C79">
-        <v>45.66228799533924</v>
+        <v>44.83496971156579</v>
       </c>
       <c r="D79">
-        <v>127.1942879953392</v>
+        <v>127.5829697115658</v>
       </c>
       <c r="E79">
-        <v>62.032</v>
+        <v>63.248</v>
       </c>
       <c r="F79">
-        <v>93.63199999999999</v>
+        <v>94.848</v>
       </c>
       <c r="G79">
         <v>12.1</v>
@@ -7893,28 +7893,28 @@
         <v>21.58</v>
       </c>
       <c r="M79">
-        <v>5.7396416</v>
+        <v>5.8141824</v>
       </c>
       <c r="N79">
-        <v>15.8403584</v>
+        <v>15.7658176</v>
       </c>
       <c r="O79">
-        <v>3.960089600000001</v>
+        <v>3.9414544</v>
       </c>
       <c r="P79">
-        <v>11.8802688</v>
+        <v>11.8243632</v>
       </c>
       <c r="Q79">
-        <v>14.1002688</v>
+        <v>14.0443632</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2356696364276405</v>
+        <v>0.2436855231330011</v>
       </c>
       <c r="T79">
-        <v>3.805682432556396</v>
+        <v>3.966350140094661</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.759816640816041</v>
+        <v>3.71161386336968</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08947131508926023</v>
+        <v>0.08933786380016316</v>
       </c>
       <c r="C80">
-        <v>44.83496971156579</v>
+        <v>44.01003418484797</v>
       </c>
       <c r="D80">
-        <v>127.5829697115658</v>
+        <v>127.974034184848</v>
       </c>
       <c r="E80">
-        <v>63.248</v>
+        <v>64.464</v>
       </c>
       <c r="F80">
-        <v>94.848</v>
+        <v>96.06399999999999</v>
       </c>
       <c r="G80">
         <v>12.1</v>
@@ -7975,28 +7975,28 @@
         <v>21.58</v>
       </c>
       <c r="M80">
-        <v>5.8141824</v>
+        <v>5.888723199999999</v>
       </c>
       <c r="N80">
-        <v>15.7658176</v>
+        <v>15.6912768</v>
       </c>
       <c r="O80">
-        <v>3.9414544</v>
+        <v>3.922819200000001</v>
       </c>
       <c r="P80">
-        <v>11.8243632</v>
+        <v>11.7684576</v>
       </c>
       <c r="Q80">
-        <v>14.0443632</v>
+        <v>13.9884576</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2436855231330011</v>
+        <v>0.2524648276198246</v>
       </c>
       <c r="T80">
-        <v>3.966350140094661</v>
+        <v>4.142319534065144</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.71161386336968</v>
+        <v>3.664631409402976</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08933786380016316</v>
+        <v>0.08920441251106608</v>
       </c>
       <c r="C81">
-        <v>44.01003418484797</v>
+        <v>43.18750339327389</v>
       </c>
       <c r="D81">
-        <v>127.974034184848</v>
+        <v>128.3675033932739</v>
       </c>
       <c r="E81">
-        <v>64.464</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="F81">
-        <v>96.06399999999999</v>
+        <v>97.28</v>
       </c>
       <c r="G81">
         <v>12.1</v>
@@ -8057,28 +8057,28 @@
         <v>21.58</v>
       </c>
       <c r="M81">
-        <v>5.888723199999999</v>
+        <v>5.963264</v>
       </c>
       <c r="N81">
-        <v>15.6912768</v>
+        <v>15.616736</v>
       </c>
       <c r="O81">
-        <v>3.922819200000001</v>
+        <v>3.904184000000001</v>
       </c>
       <c r="P81">
-        <v>11.7684576</v>
+        <v>11.712552</v>
       </c>
       <c r="Q81">
-        <v>13.9884576</v>
+        <v>13.932552</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2524648276198246</v>
+        <v>0.2621220625553304</v>
       </c>
       <c r="T81">
-        <v>4.142319534065144</v>
+        <v>4.335885867432674</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.664631409402976</v>
+        <v>3.618823516785439</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08920441251106608</v>
+        <v>0.089070961221969</v>
       </c>
       <c r="C82">
-        <v>43.18750339327389</v>
+        <v>42.36739958606076</v>
       </c>
       <c r="D82">
-        <v>128.3675033932739</v>
+        <v>128.7633995860608</v>
       </c>
       <c r="E82">
-        <v>65.68000000000001</v>
+        <v>66.896</v>
       </c>
       <c r="F82">
-        <v>97.28</v>
+        <v>98.496</v>
       </c>
       <c r="G82">
         <v>12.1</v>
@@ -8139,28 +8139,28 @@
         <v>21.58</v>
       </c>
       <c r="M82">
-        <v>5.963264</v>
+        <v>6.0378048</v>
       </c>
       <c r="N82">
-        <v>15.616736</v>
+        <v>15.5421952</v>
       </c>
       <c r="O82">
-        <v>3.904184000000001</v>
+        <v>3.8855488</v>
       </c>
       <c r="P82">
-        <v>11.712552</v>
+        <v>11.6566464</v>
       </c>
       <c r="Q82">
-        <v>13.932552</v>
+        <v>13.8766464</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2621220625553304</v>
+        <v>0.272795848536679</v>
       </c>
       <c r="T82">
-        <v>4.335885867432674</v>
+        <v>4.549827604312576</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.618823516785439</v>
+        <v>3.574146683244878</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.089070961221969</v>
+        <v>0.08893750993287192</v>
       </c>
       <c r="C83">
-        <v>42.36739958606076</v>
+        <v>41.54974528774876</v>
       </c>
       <c r="D83">
-        <v>128.7633995860608</v>
+        <v>129.1617452877488</v>
       </c>
       <c r="E83">
-        <v>66.896</v>
+        <v>68.11200000000001</v>
       </c>
       <c r="F83">
-        <v>98.496</v>
+        <v>99.712</v>
       </c>
       <c r="G83">
         <v>12.1</v>
@@ -8221,28 +8221,28 @@
         <v>21.58</v>
       </c>
       <c r="M83">
-        <v>6.0378048</v>
+        <v>6.1123456</v>
       </c>
       <c r="N83">
-        <v>15.5421952</v>
+        <v>15.4676544</v>
       </c>
       <c r="O83">
-        <v>3.8855488</v>
+        <v>3.8669136</v>
       </c>
       <c r="P83">
-        <v>11.6566464</v>
+        <v>11.6007408</v>
       </c>
       <c r="Q83">
-        <v>13.8766464</v>
+        <v>13.8207408</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.272795848536679</v>
+        <v>0.2846556107381774</v>
       </c>
       <c r="T83">
-        <v>4.549827604312576</v>
+        <v>4.787540645290245</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.574146683244878</v>
+        <v>3.53055952857116</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08893750993287192</v>
+        <v>0.09054705864377484</v>
       </c>
       <c r="C84">
-        <v>41.54974528774876</v>
+        <v>35.68780593605041</v>
       </c>
       <c r="D84">
-        <v>129.1617452877488</v>
+        <v>124.5158059360504</v>
       </c>
       <c r="E84">
-        <v>68.11200000000001</v>
+        <v>69.328</v>
       </c>
       <c r="F84">
-        <v>99.712</v>
+        <v>100.928</v>
       </c>
       <c r="G84">
         <v>12.1</v>
@@ -8303,45 +8303,45 @@
         <v>21.58</v>
       </c>
       <c r="M84">
-        <v>6.1123456</v>
+        <v>6.4694848</v>
       </c>
       <c r="N84">
-        <v>15.4676544</v>
+        <v>15.1105152</v>
       </c>
       <c r="O84">
-        <v>3.8669136</v>
+        <v>3.7776288</v>
       </c>
       <c r="P84">
-        <v>11.6007408</v>
+        <v>11.3328864</v>
       </c>
       <c r="Q84">
-        <v>13.8207408</v>
+        <v>13.5528864</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2846556107381774</v>
+        <v>0.2979106390810285</v>
       </c>
       <c r="T84">
-        <v>4.787540645290245</v>
+        <v>5.053219926382934</v>
       </c>
       <c r="U84">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V84">
         <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y84">
-        <v>3.53055952857116</v>
+        <v>3.335659742179161</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09054705864377484</v>
+        <v>0.09043460735467776</v>
       </c>
       <c r="C85">
-        <v>35.68780593605041</v>
+        <v>34.78550787542687</v>
       </c>
       <c r="D85">
-        <v>124.5158059360504</v>
+        <v>124.8295078754269</v>
       </c>
       <c r="E85">
-        <v>69.328</v>
+        <v>70.54400000000001</v>
       </c>
       <c r="F85">
-        <v>100.928</v>
+        <v>102.144</v>
       </c>
       <c r="G85">
         <v>12.1</v>
@@ -8385,28 +8385,28 @@
         <v>21.58</v>
       </c>
       <c r="M85">
-        <v>6.4694848</v>
+        <v>6.547430400000001</v>
       </c>
       <c r="N85">
-        <v>15.1105152</v>
+        <v>15.0325696</v>
       </c>
       <c r="O85">
-        <v>3.7776288</v>
+        <v>3.758142400000001</v>
       </c>
       <c r="P85">
-        <v>11.3328864</v>
+        <v>11.2744272</v>
       </c>
       <c r="Q85">
-        <v>13.5528864</v>
+        <v>13.4944272</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2979106390810285</v>
+        <v>0.3128225459667361</v>
       </c>
       <c r="T85">
-        <v>5.053219926382934</v>
+        <v>5.352109117612209</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.335659742179161</v>
+        <v>3.295949507153219</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09043460735467776</v>
+        <v>0.09032215606558068</v>
       </c>
       <c r="C86">
-        <v>34.78550787542689</v>
+        <v>33.88479447244769</v>
       </c>
       <c r="D86">
-        <v>124.8295078754269</v>
+        <v>125.1447944724477</v>
       </c>
       <c r="E86">
-        <v>70.544</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="F86">
-        <v>102.144</v>
+        <v>103.36</v>
       </c>
       <c r="G86">
         <v>12.1</v>
@@ -8467,28 +8467,28 @@
         <v>21.58</v>
       </c>
       <c r="M86">
-        <v>6.5474304</v>
+        <v>6.625376</v>
       </c>
       <c r="N86">
-        <v>15.0325696</v>
+        <v>14.954624</v>
       </c>
       <c r="O86">
-        <v>3.758142400000001</v>
+        <v>3.738656000000001</v>
       </c>
       <c r="P86">
-        <v>11.2744272</v>
+        <v>11.215968</v>
       </c>
       <c r="Q86">
-        <v>13.4944272</v>
+        <v>13.435968</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3128225459667359</v>
+        <v>0.3297227071038711</v>
       </c>
       <c r="T86">
-        <v>5.352109117612206</v>
+        <v>5.690850201005384</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.295949507153219</v>
+        <v>3.257173630598475</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09032215606558068</v>
+        <v>0.0902097047764836</v>
       </c>
       <c r="C87">
-        <v>33.88479447244769</v>
+        <v>32.98567776480564</v>
       </c>
       <c r="D87">
-        <v>125.1447944724477</v>
+        <v>125.4616777648056</v>
       </c>
       <c r="E87">
-        <v>71.76000000000001</v>
+        <v>72.976</v>
       </c>
       <c r="F87">
-        <v>103.36</v>
+        <v>104.576</v>
       </c>
       <c r="G87">
         <v>12.1</v>
@@ -8549,28 +8549,28 @@
         <v>21.58</v>
       </c>
       <c r="M87">
-        <v>6.625376</v>
+        <v>6.7033216</v>
       </c>
       <c r="N87">
-        <v>14.954624</v>
+        <v>14.8766784</v>
       </c>
       <c r="O87">
-        <v>3.738656000000001</v>
+        <v>3.719169600000001</v>
       </c>
       <c r="P87">
-        <v>11.215968</v>
+        <v>11.1575088</v>
       </c>
       <c r="Q87">
-        <v>13.435968</v>
+        <v>13.3775088</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3297227071038711</v>
+        <v>0.3490371769748827</v>
       </c>
       <c r="T87">
-        <v>5.690850201005384</v>
+        <v>6.077982867740443</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.257173630598475</v>
+        <v>3.219299518614772</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.0902097047764836</v>
+        <v>0.09009725348738651</v>
       </c>
       <c r="C88">
-        <v>32.98567776480564</v>
+        <v>32.08816991242725</v>
       </c>
       <c r="D88">
-        <v>125.4616777648056</v>
+        <v>125.7801699124272</v>
       </c>
       <c r="E88">
-        <v>72.976</v>
+        <v>74.19200000000001</v>
       </c>
       <c r="F88">
-        <v>104.576</v>
+        <v>105.792</v>
       </c>
       <c r="G88">
         <v>12.1</v>
@@ -8631,28 +8631,28 @@
         <v>21.58</v>
       </c>
       <c r="M88">
-        <v>6.7033216</v>
+        <v>6.7812672</v>
       </c>
       <c r="N88">
-        <v>14.8766784</v>
+        <v>14.7987328</v>
       </c>
       <c r="O88">
-        <v>3.719169600000001</v>
+        <v>3.6996832</v>
       </c>
       <c r="P88">
-        <v>11.1575088</v>
+        <v>11.0990496</v>
       </c>
       <c r="Q88">
-        <v>13.3775088</v>
+        <v>13.3190496</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3490371769748827</v>
+        <v>0.3713231037491269</v>
       </c>
       <c r="T88">
-        <v>6.077982867740443</v>
+        <v>6.524674406280897</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.219299518614772</v>
+        <v>3.182296075872073</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09009725348738651</v>
+        <v>0.08998480219828943</v>
       </c>
       <c r="C89">
-        <v>32.08816991242725</v>
+        <v>31.19228319902807</v>
       </c>
       <c r="D89">
-        <v>125.7801699124272</v>
+        <v>126.1002831990281</v>
       </c>
       <c r="E89">
-        <v>74.19200000000001</v>
+        <v>75.408</v>
       </c>
       <c r="F89">
-        <v>105.792</v>
+        <v>107.008</v>
       </c>
       <c r="G89">
         <v>12.1</v>
@@ -8713,28 +8713,28 @@
         <v>21.58</v>
       </c>
       <c r="M89">
-        <v>6.7812672</v>
+        <v>6.8592128</v>
       </c>
       <c r="N89">
-        <v>14.7987328</v>
+        <v>14.7207872</v>
       </c>
       <c r="O89">
-        <v>3.6996832</v>
+        <v>3.6801968</v>
       </c>
       <c r="P89">
-        <v>11.0990496</v>
+        <v>11.0405904</v>
       </c>
       <c r="Q89">
-        <v>13.3190496</v>
+        <v>13.2605904</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3713231037491269</v>
+        <v>0.3973233516524119</v>
       </c>
       <c r="T89">
-        <v>6.524674406280897</v>
+        <v>7.045814534578095</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.182296075872073</v>
+        <v>3.146133620464436</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08998480219828943</v>
+        <v>0.08987235090919235</v>
       </c>
       <c r="C90">
-        <v>31.19228319902807</v>
+        <v>30.29803003369216</v>
       </c>
       <c r="D90">
-        <v>126.1002831990281</v>
+        <v>126.4220300336922</v>
       </c>
       <c r="E90">
-        <v>75.408</v>
+        <v>76.624</v>
       </c>
       <c r="F90">
-        <v>107.008</v>
+        <v>108.224</v>
       </c>
       <c r="G90">
         <v>12.1</v>
@@ -8795,28 +8795,28 @@
         <v>21.58</v>
       </c>
       <c r="M90">
-        <v>6.8592128</v>
+        <v>6.9371584</v>
       </c>
       <c r="N90">
-        <v>14.7207872</v>
+        <v>14.6428416</v>
       </c>
       <c r="O90">
-        <v>3.6801968</v>
+        <v>3.660710400000001</v>
       </c>
       <c r="P90">
-        <v>11.0405904</v>
+        <v>10.9821312</v>
       </c>
       <c r="Q90">
-        <v>13.2605904</v>
+        <v>13.2021312</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3973233516524119</v>
+        <v>0.428050917356294</v>
       </c>
       <c r="T90">
-        <v>7.045814534578095</v>
+        <v>7.661707413474781</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.146133620464436</v>
+        <v>3.110783804504162</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08987235090919235</v>
+        <v>0.08975989962009527</v>
       </c>
       <c r="C91">
-        <v>30.29803003369216</v>
+        <v>29.40542295247533</v>
       </c>
       <c r="D91">
-        <v>126.4220300336922</v>
+        <v>126.7454229524753</v>
       </c>
       <c r="E91">
-        <v>76.624</v>
+        <v>77.84</v>
       </c>
       <c r="F91">
-        <v>108.224</v>
+        <v>109.44</v>
       </c>
       <c r="G91">
         <v>12.1</v>
@@ -8877,28 +8877,28 @@
         <v>21.58</v>
       </c>
       <c r="M91">
-        <v>6.9371584</v>
+        <v>7.015104</v>
       </c>
       <c r="N91">
-        <v>14.6428416</v>
+        <v>14.564896</v>
       </c>
       <c r="O91">
-        <v>3.660710400000001</v>
+        <v>3.641224</v>
       </c>
       <c r="P91">
-        <v>10.9821312</v>
+        <v>10.923672</v>
       </c>
       <c r="Q91">
-        <v>13.2021312</v>
+        <v>13.143672</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.428050917356294</v>
+        <v>0.4649239962009527</v>
       </c>
       <c r="T91">
-        <v>7.661707413474781</v>
+        <v>8.400778868150807</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.110783804504162</v>
+        <v>3.076219540009671</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08975989962009527</v>
+        <v>0.08964744833099819</v>
       </c>
       <c r="C92">
-        <v>29.40542295247533</v>
+        <v>28.51447462003348</v>
       </c>
       <c r="D92">
-        <v>126.7454229524753</v>
+        <v>127.0704746200335</v>
       </c>
       <c r="E92">
-        <v>77.84</v>
+        <v>79.056</v>
       </c>
       <c r="F92">
-        <v>109.44</v>
+        <v>110.656</v>
       </c>
       <c r="G92">
         <v>12.1</v>
@@ -8959,28 +8959,28 @@
         <v>21.58</v>
       </c>
       <c r="M92">
-        <v>7.015104</v>
+        <v>7.0930496</v>
       </c>
       <c r="N92">
-        <v>14.564896</v>
+        <v>14.4869504</v>
       </c>
       <c r="O92">
-        <v>3.641224</v>
+        <v>3.6217376</v>
       </c>
       <c r="P92">
-        <v>10.923672</v>
+        <v>10.8652128</v>
       </c>
       <c r="Q92">
-        <v>13.143672</v>
+        <v>13.0852128</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4649239962009527</v>
+        <v>0.5099910925666465</v>
       </c>
       <c r="T92">
-        <v>8.400778868150807</v>
+        <v>9.304088423865947</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.076219540009671</v>
+        <v>3.042414929679894</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08964744833099819</v>
+        <v>0.0895349970419011</v>
       </c>
       <c r="C93">
-        <v>28.51447462003348</v>
+        <v>27.62519783127577</v>
       </c>
       <c r="D93">
-        <v>127.0704746200335</v>
+        <v>127.3971978312758</v>
       </c>
       <c r="E93">
-        <v>79.056</v>
+        <v>80.27200000000001</v>
       </c>
       <c r="F93">
-        <v>110.656</v>
+        <v>111.872</v>
       </c>
       <c r="G93">
         <v>12.1</v>
@@ -9041,28 +9041,28 @@
         <v>21.58</v>
       </c>
       <c r="M93">
-        <v>7.0930496</v>
+        <v>7.1709952</v>
       </c>
       <c r="N93">
-        <v>14.4869504</v>
+        <v>14.4090048</v>
       </c>
       <c r="O93">
-        <v>3.6217376</v>
+        <v>3.6022512</v>
       </c>
       <c r="P93">
-        <v>10.8652128</v>
+        <v>10.8067536</v>
       </c>
       <c r="Q93">
-        <v>13.0852128</v>
+        <v>13.0267536</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5099910925666465</v>
+        <v>0.566324963023764</v>
       </c>
       <c r="T93">
-        <v>9.304088423865947</v>
+        <v>10.43322536850988</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.042414929679894</v>
+        <v>3.009345202183374</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0895349970419011</v>
+        <v>0.09486304575280402</v>
       </c>
       <c r="C94">
-        <v>27.62519783127577</v>
+        <v>12.57437642419301</v>
       </c>
       <c r="D94">
-        <v>127.3971978312758</v>
+        <v>113.562376424193</v>
       </c>
       <c r="E94">
-        <v>80.27200000000001</v>
+        <v>81.488</v>
       </c>
       <c r="F94">
-        <v>111.872</v>
+        <v>113.088</v>
       </c>
       <c r="G94">
         <v>12.1</v>
@@ -9123,45 +9123,45 @@
         <v>21.58</v>
       </c>
       <c r="M94">
-        <v>7.1709952</v>
+        <v>8.1310272</v>
       </c>
       <c r="N94">
-        <v>14.4090048</v>
+        <v>13.4489728</v>
       </c>
       <c r="O94">
-        <v>3.6022512</v>
+        <v>3.3622432</v>
       </c>
       <c r="P94">
-        <v>10.8067536</v>
+        <v>10.0867296</v>
       </c>
       <c r="Q94">
-        <v>13.0267536</v>
+        <v>12.3067296</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.566324963023764</v>
+        <v>0.6387542250400577</v>
       </c>
       <c r="T94">
-        <v>10.43322536850988</v>
+        <v>11.88497286876635</v>
       </c>
       <c r="U94">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V94">
         <v>0.25</v>
       </c>
       <c r="W94">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y94">
-        <v>3.009345202183374</v>
+        <v>2.654031215145856</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09486304575280402</v>
+        <v>0.09480909446370693</v>
       </c>
       <c r="C95">
-        <v>12.57437642419301</v>
+        <v>11.48339070303366</v>
       </c>
       <c r="D95">
-        <v>113.562376424193</v>
+        <v>113.6873907030337</v>
       </c>
       <c r="E95">
-        <v>81.488</v>
+        <v>82.70400000000001</v>
       </c>
       <c r="F95">
-        <v>113.088</v>
+        <v>114.304</v>
       </c>
       <c r="G95">
         <v>12.1</v>
@@ -9205,28 +9205,28 @@
         <v>21.58</v>
       </c>
       <c r="M95">
-        <v>8.1310272</v>
+        <v>8.218457600000001</v>
       </c>
       <c r="N95">
-        <v>13.4489728</v>
+        <v>13.3615424</v>
       </c>
       <c r="O95">
-        <v>3.3622432</v>
+        <v>3.3403856</v>
       </c>
       <c r="P95">
-        <v>10.0867296</v>
+        <v>10.0211568</v>
       </c>
       <c r="Q95">
-        <v>12.3067296</v>
+        <v>12.2411568</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6387542250400577</v>
+        <v>0.7353265743951162</v>
       </c>
       <c r="T95">
-        <v>11.88497286876635</v>
+        <v>13.82063620244166</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.654031215145856</v>
+        <v>2.625796840516644</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09480909446370693</v>
+        <v>0.09475514317460985</v>
       </c>
       <c r="C96">
-        <v>11.48339070303366</v>
+        <v>10.39268052724344</v>
       </c>
       <c r="D96">
-        <v>113.6873907030337</v>
+        <v>113.8126805272434</v>
       </c>
       <c r="E96">
-        <v>82.70400000000001</v>
+        <v>83.92</v>
       </c>
       <c r="F96">
-        <v>114.304</v>
+        <v>115.52</v>
       </c>
       <c r="G96">
         <v>12.1</v>
@@ -9287,28 +9287,28 @@
         <v>21.58</v>
       </c>
       <c r="M96">
-        <v>8.218457600000001</v>
+        <v>8.305887999999999</v>
       </c>
       <c r="N96">
-        <v>13.3615424</v>
+        <v>13.274112</v>
       </c>
       <c r="O96">
-        <v>3.3403856</v>
+        <v>3.318528000000001</v>
       </c>
       <c r="P96">
-        <v>10.0211568</v>
+        <v>9.955584000000002</v>
       </c>
       <c r="Q96">
-        <v>12.2411568</v>
+        <v>12.175584</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7353265743951162</v>
+        <v>0.8705278634921982</v>
       </c>
       <c r="T96">
-        <v>13.82063620244166</v>
+        <v>16.53056486958709</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.625796840516644</v>
+        <v>2.598156873774364</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09475514317460985</v>
+        <v>0.09470119188551276</v>
       </c>
       <c r="C97">
-        <v>10.39268052724344</v>
+        <v>9.302246808826439</v>
       </c>
       <c r="D97">
-        <v>113.8126805272434</v>
+        <v>113.9382468088264</v>
       </c>
       <c r="E97">
-        <v>83.92</v>
+        <v>85.13600000000001</v>
       </c>
       <c r="F97">
-        <v>115.52</v>
+        <v>116.736</v>
       </c>
       <c r="G97">
         <v>12.1</v>
@@ -9369,28 +9369,28 @@
         <v>21.58</v>
       </c>
       <c r="M97">
-        <v>8.305887999999999</v>
+        <v>8.3933184</v>
       </c>
       <c r="N97">
-        <v>13.274112</v>
+        <v>13.1866816</v>
       </c>
       <c r="O97">
-        <v>3.318528000000001</v>
+        <v>3.2966704</v>
       </c>
       <c r="P97">
-        <v>9.955584000000002</v>
+        <v>9.890011200000002</v>
       </c>
       <c r="Q97">
-        <v>12.175584</v>
+        <v>12.1100112</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8705278634921982</v>
+        <v>1.073329797137821</v>
       </c>
       <c r="T97">
-        <v>16.53056486958709</v>
+        <v>20.59545787030524</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.598156873774364</v>
+        <v>2.571092739672547</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09470119188551279</v>
+        <v>0.09464724059641569</v>
       </c>
       <c r="C98">
-        <v>9.302246808826382</v>
+        <v>8.212090463815784</v>
       </c>
       <c r="D98">
-        <v>113.9382468088264</v>
+        <v>114.0640904638158</v>
       </c>
       <c r="E98">
-        <v>85.136</v>
+        <v>86.352</v>
       </c>
       <c r="F98">
-        <v>116.736</v>
+        <v>117.952</v>
       </c>
       <c r="G98">
         <v>12.1</v>
@@ -9451,28 +9451,28 @@
         <v>21.58</v>
       </c>
       <c r="M98">
-        <v>8.3933184</v>
+        <v>8.480748800000001</v>
       </c>
       <c r="N98">
-        <v>13.1866816</v>
+        <v>13.0992512</v>
       </c>
       <c r="O98">
-        <v>3.2966704</v>
+        <v>3.2748128</v>
       </c>
       <c r="P98">
-        <v>9.890011200000002</v>
+        <v>9.824438400000002</v>
       </c>
       <c r="Q98">
-        <v>12.1100112</v>
+        <v>12.0444384</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.073329797137819</v>
+        <v>1.411333019880522</v>
       </c>
       <c r="T98">
-        <v>20.59545787030518</v>
+        <v>27.37027953816873</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.571092739672547</v>
+        <v>2.544586628954273</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09464724059641569</v>
+        <v>0.09459328930731861</v>
       </c>
       <c r="C99">
-        <v>8.212090463815784</v>
+        <v>7.122212412296236</v>
       </c>
       <c r="D99">
-        <v>114.0640904638158</v>
+        <v>114.1902124122962</v>
       </c>
       <c r="E99">
-        <v>86.352</v>
+        <v>87.568</v>
       </c>
       <c r="F99">
-        <v>117.952</v>
+        <v>119.168</v>
       </c>
       <c r="G99">
         <v>12.1</v>
@@ -9533,28 +9533,28 @@
         <v>21.58</v>
       </c>
       <c r="M99">
-        <v>8.480748800000001</v>
+        <v>8.568179199999999</v>
       </c>
       <c r="N99">
-        <v>13.0992512</v>
+        <v>13.0118208</v>
       </c>
       <c r="O99">
-        <v>3.2748128</v>
+        <v>3.252955200000001</v>
       </c>
       <c r="P99">
-        <v>9.824438400000002</v>
+        <v>9.758865600000002</v>
       </c>
       <c r="Q99">
-        <v>12.0444384</v>
+        <v>11.9788656</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.411333019880522</v>
+        <v>2.087339465365929</v>
       </c>
       <c r="T99">
-        <v>27.37027953816873</v>
+        <v>40.91992287389583</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.544586628954273</v>
+        <v>2.518621459271067</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09459328930731861</v>
+        <v>0.09743508801822154</v>
       </c>
       <c r="C100">
-        <v>7.122212412296236</v>
+        <v>-0.3783822477628433</v>
       </c>
       <c r="D100">
-        <v>114.1902124122962</v>
+        <v>107.9056177522372</v>
       </c>
       <c r="E100">
-        <v>87.568</v>
+        <v>88.78400000000001</v>
       </c>
       <c r="F100">
-        <v>119.168</v>
+        <v>120.384</v>
       </c>
       <c r="G100">
         <v>12.1</v>
@@ -9615,129 +9615,47 @@
         <v>21.58</v>
       </c>
       <c r="M100">
-        <v>8.568179199999999</v>
+        <v>9.1251072</v>
       </c>
       <c r="N100">
-        <v>13.0118208</v>
+        <v>12.4548928</v>
       </c>
       <c r="O100">
-        <v>3.252955200000001</v>
+        <v>3.1137232</v>
       </c>
       <c r="P100">
-        <v>9.758865600000002</v>
+        <v>9.341169600000001</v>
       </c>
       <c r="Q100">
-        <v>11.9788656</v>
+        <v>11.5611696</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.087339465365929</v>
+        <v>4.11535880182215</v>
       </c>
       <c r="T100">
-        <v>40.91992287389583</v>
+        <v>81.56885288107711</v>
       </c>
       <c r="U100">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V100">
         <v>0.25</v>
       </c>
       <c r="W100">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y100">
-        <v>2.518621459271067</v>
+        <v>2.364903724089948</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09743508801822154</v>
-      </c>
-      <c r="C101">
-        <v>-0.3783822477628433</v>
-      </c>
-      <c r="D101">
-        <v>107.9056177522372</v>
-      </c>
-      <c r="E101">
-        <v>88.78400000000001</v>
-      </c>
-      <c r="F101">
-        <v>120.384</v>
-      </c>
-      <c r="G101">
-        <v>12.1</v>
-      </c>
-      <c r="H101">
-        <v>90</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>23.8</v>
-      </c>
-      <c r="K101">
-        <v>2.22</v>
-      </c>
-      <c r="L101">
-        <v>21.58</v>
-      </c>
-      <c r="M101">
-        <v>9.1251072</v>
-      </c>
-      <c r="N101">
-        <v>12.4548928</v>
-      </c>
-      <c r="O101">
-        <v>3.1137232</v>
-      </c>
-      <c r="P101">
-        <v>9.341169600000001</v>
-      </c>
-      <c r="Q101">
-        <v>11.5611696</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.11535880182215</v>
-      </c>
-      <c r="T101">
-        <v>81.56885288107711</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.364903724089948</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
